--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\6574114\PycharmProjects\PyHubProductive\mes_north_sea\clean_data\new_technologies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9829078-CDDB-418C-AF0C-12B24345D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -712,23 +712,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="15.33203125" customWidth="1"/>
     <col min="11" max="11" width="43" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="34" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="43" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="25" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="24" customWidth="1"/>
-    <col min="18" max="18" width="15.28515625" customWidth="1"/>
+    <col min="18" max="18" width="15.33203125" customWidth="1"/>
     <col min="20" max="20" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -822,7 +822,7 @@
         <v>All_no_onshore_wind</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -866,7 +866,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -910,7 +910,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -954,7 +954,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -998,7 +998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>68</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -4544,13 +4544,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4641E15-13AD-4645-88BC-55D8D2E876ED}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>74</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>'RE_only': 'RE only',</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>'Battery_on': 'Battery (onshore only)',</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>'Battery_off': 'Battery (offshore only)',</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>'Battery_all': 'Battery (all)',</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>'ElectricityGrid_all': 'Grid Expansion (all)',</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>'Hydrogen_Baseline': 'Hydrogen (all)',</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>'Hydrogen_H1': 'Hydrogen (no storage)',</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>'Hydrogen_H2': 'Hydrogen (no hydrogen offshore)',</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>'Hydrogen_H3': 'Hydrogen (no hydrogen onshore)',</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>'Hydrogen_H4': 'Hydrogen (local use only)',</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>'All': 'All Pathways',</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>'RE_only_no_onshore_wind': 'RE only - no onshore wind',</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>'Battery_on_no_onshore_wind': 'Battery (onshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>'Battery_off_no_onshore_wind': 'Battery (offshore only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>'Battery_all_no_onshore_wind': 'Battery (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>'ElectricityGrid_all_no_onshore_wind': 'Grid Expansion (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>'Hydrogen_Baseline_no_onshore_wind': 'Hydrogen (all) - no onshore wind',</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>'Hydrogen_H1_no_onshore_wind': 'Hydrogen (no storage) - no onshore wind',</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>'Hydrogen_H2_no_onshore_wind': 'Hydrogen (no hydrogen offshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>'Hydrogen_H3_no_onshore_wind': 'Hydrogen (no hydrogen onshore) - no onshore wind',</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>'Hydrogen_H4_no_onshore_wind': 'Hydrogen (local use only) - no onshore wind',</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>77</v>
       </c>

--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9829078-CDDB-418C-AF0C-12B24345D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A608C226-952A-E148-83A1-11182C0F67E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="118">
   <si>
     <t>Electrolyser_PEM_offshore</t>
   </si>
@@ -388,6 +388,12 @@
   </si>
   <si>
     <t>ElectricityGrid_noBorder</t>
+  </si>
+  <si>
+    <t>PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>Onshore_Wind, PV, DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
   </si>
 </sst>
 </file>
@@ -1357,6 +1363,9 @@
       <c r="B14" t="s">
         <v>1</v>
       </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
       <c r="E14" t="s">
         <v>45</v>
       </c>
@@ -1401,6 +1410,9 @@
       <c r="B15" t="s">
         <v>1</v>
       </c>
+      <c r="C15" t="s">
+        <v>116</v>
+      </c>
       <c r="E15" t="s">
         <v>45</v>
       </c>
@@ -1445,6 +1457,9 @@
       <c r="B16" t="s">
         <v>1</v>
       </c>
+      <c r="C16" t="s">
+        <v>116</v>
+      </c>
       <c r="E16" t="s">
         <v>45</v>
       </c>
@@ -1489,6 +1504,9 @@
       <c r="B17" t="s">
         <v>1</v>
       </c>
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
@@ -1533,6 +1551,9 @@
       <c r="B18" t="s">
         <v>1</v>
       </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
@@ -1577,6 +1598,9 @@
       <c r="B19" t="s">
         <v>1</v>
       </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
@@ -1621,6 +1645,9 @@
       <c r="B20" t="s">
         <v>1</v>
       </c>
+      <c r="C20" t="s">
+        <v>116</v>
+      </c>
       <c r="E20" t="s">
         <v>45</v>
       </c>
@@ -1665,6 +1692,9 @@
       <c r="B21" t="s">
         <v>1</v>
       </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
       <c r="E21" t="s">
         <v>45</v>
       </c>
@@ -1709,6 +1739,9 @@
       <c r="B22" t="s">
         <v>1</v>
       </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
       <c r="E22" t="s">
         <v>45</v>
       </c>
@@ -1753,6 +1786,9 @@
       <c r="B23" t="s">
         <v>1</v>
       </c>
+      <c r="C23" t="s">
+        <v>116</v>
+      </c>
       <c r="E23" t="s">
         <v>45</v>
       </c>
@@ -1798,7 +1834,7 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>70</v>
@@ -1881,7 +1917,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
         <v>70</v>
@@ -1964,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
         <v>70</v>
@@ -2047,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>70</v>
@@ -2130,7 +2166,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>70</v>
@@ -2213,7 +2249,7 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
         <v>70</v>
@@ -2296,7 +2332,7 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
         <v>70</v>
@@ -2379,7 +2415,7 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>70</v>
@@ -2462,7 +2498,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
         <v>70</v>
@@ -2545,7 +2581,7 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
         <v>70</v>
@@ -2628,7 +2664,7 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
         <v>70</v>
@@ -2711,7 +2747,7 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
         <v>70</v>
@@ -2794,7 +2830,7 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
@@ -2877,7 +2913,7 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D37" t="s">
         <v>70</v>
@@ -2960,7 +2996,7 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
         <v>70</v>
@@ -3043,7 +3079,7 @@
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D39" t="s">
         <v>70</v>

--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A608C226-952A-E148-83A1-11182C0F67E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5817A44-D7F0-5648-B775-D427B5454F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="125">
   <si>
     <t>Electrolyser_PEM_offshore</t>
   </si>
@@ -390,10 +390,31 @@
     <t>ElectricityGrid_noBorder</t>
   </si>
   <si>
+    <t>Onshore_Wind, PV, DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
+  </si>
+  <si>
+    <t>DK_ST1</t>
+  </si>
+  <si>
+    <t>NO_ST2</t>
+  </si>
+  <si>
+    <t>DK_ST2</t>
+  </si>
+  <si>
+    <t>NO_ST1</t>
+  </si>
+  <si>
+    <t>New_CO2_Storage_2040</t>
+  </si>
+  <si>
     <t>PermanentStorage_CO2_simple</t>
   </si>
   <si>
-    <t>Onshore_Wind, PV, DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
+    <t>DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
   </si>
 </sst>
 </file>
@@ -717,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA56"/>
+  <dimension ref="A1:AA60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -1364,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
@@ -1411,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -1458,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
@@ -1505,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -1552,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
@@ -1599,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
@@ -1646,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
@@ -1693,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
@@ -1740,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -1787,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
@@ -1834,7 +1855,7 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
         <v>70</v>
@@ -1917,7 +1938,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>70</v>
@@ -2000,7 +2021,7 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
         <v>70</v>
@@ -2083,7 +2104,7 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
         <v>70</v>
@@ -2166,7 +2187,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>70</v>
@@ -2249,7 +2270,7 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>70</v>
@@ -2332,7 +2353,7 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>70</v>
@@ -2415,7 +2436,7 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
         <v>70</v>
@@ -2498,7 +2519,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
         <v>70</v>
@@ -2581,7 +2602,7 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
         <v>70</v>
@@ -2664,7 +2685,7 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>70</v>
@@ -2747,7 +2768,7 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
         <v>70</v>
@@ -2830,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
@@ -2913,7 +2934,7 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
         <v>70</v>
@@ -2996,7 +3017,7 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D38" t="s">
         <v>70</v>
@@ -3079,7 +3100,7 @@
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D39" t="s">
         <v>70</v>
@@ -3162,7 +3183,7 @@
         <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
         <v>49</v>
@@ -3245,7 +3266,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D41" t="s">
         <v>49</v>
@@ -3328,7 +3349,7 @@
         <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D42" t="s">
         <v>49</v>
@@ -3411,7 +3432,7 @@
         <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D43" t="s">
         <v>49</v>
@@ -3494,7 +3515,7 @@
         <v>64</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
         <v>49</v>
@@ -3577,7 +3598,7 @@
         <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D45" t="s">
         <v>49</v>
@@ -3660,7 +3681,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D46" t="s">
         <v>49</v>
@@ -3743,7 +3764,7 @@
         <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
@@ -3826,7 +3847,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
         <v>49</v>
@@ -3909,7 +3930,7 @@
         <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
         <v>49</v>
@@ -3992,7 +4013,7 @@
         <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
         <v>49</v>
@@ -4075,7 +4096,7 @@
         <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
         <v>49</v>
@@ -4158,7 +4179,7 @@
         <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D52" t="s">
         <v>49</v>
@@ -4241,7 +4262,7 @@
         <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
         <v>49</v>
@@ -4324,7 +4345,7 @@
         <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
         <v>49</v>
@@ -4407,7 +4428,7 @@
         <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
         <v>49</v>
@@ -4490,7 +4511,7 @@
         <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
         <v>49</v>
@@ -4563,6 +4584,50 @@
       </c>
       <c r="AA56" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5817A44-D7F0-5648-B775-D427B5454F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EF4A96-354F-EF47-9CA6-64870252A183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="1280" yWindow="500" windowWidth="27520" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="127">
   <si>
     <t>Electrolyser_PEM_offshore</t>
   </si>
@@ -396,9 +396,21 @@
     <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
   </si>
   <si>
+    <t>DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
+  </si>
+  <si>
+    <t>DAC_Adsorption_offshore, HeatPump_AirSourced_offshore, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_AirSourced_offshore, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
     <t>DK_ST1</t>
   </si>
   <si>
+    <t>New_CO2_Storage_2040</t>
+  </si>
+  <si>
     <t>NO_ST2</t>
   </si>
   <si>
@@ -408,20 +420,14 @@
     <t>NO_ST1</t>
   </si>
   <si>
-    <t>New_CO2_Storage_2040</t>
-  </si>
-  <si>
-    <t>PermanentStorage_CO2_simple</t>
-  </si>
-  <si>
-    <t>DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
+    <t>PermanentStorage_CO2_simple, DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,6 +441,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -444,7 +457,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -452,12 +465,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1164,6 +1190,9 @@
       <c r="B9" t="s">
         <v>2</v>
       </c>
+      <c r="C9" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="E9" t="s">
         <v>45</v>
       </c>
@@ -1252,6 +1281,9 @@
       <c r="B11" t="s">
         <v>2</v>
       </c>
+      <c r="C11" t="s">
+        <v>126</v>
+      </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
@@ -1296,6 +1328,9 @@
       <c r="B12" t="s">
         <v>2</v>
       </c>
+      <c r="C12" t="s">
+        <v>126</v>
+      </c>
       <c r="E12" t="s">
         <v>45</v>
       </c>
@@ -1340,6 +1375,9 @@
       <c r="B13" t="s">
         <v>2</v>
       </c>
+      <c r="C13" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
@@ -1385,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
@@ -1432,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -1479,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
@@ -1526,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -1573,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
@@ -1620,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
@@ -1667,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
@@ -1714,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
@@ -1761,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -1808,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
@@ -3764,7 +3802,7 @@
         <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
@@ -3930,7 +3968,7 @@
         <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D49" t="s">
         <v>49</v>
@@ -4013,7 +4051,7 @@
         <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
         <v>49</v>
@@ -4179,7 +4217,7 @@
         <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
         <v>49</v>
@@ -4262,7 +4300,7 @@
         <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D53" t="s">
         <v>49</v>
@@ -4588,46 +4626,46 @@
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>118</v>
-      </c>
-      <c r="B57" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>119</v>
-      </c>
-      <c r="B58" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C58" t="s">
-        <v>123</v>
+      <c r="C58" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>120</v>
-      </c>
-      <c r="B59" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C59" t="s">
-        <v>123</v>
+      <c r="C59" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>121</v>
-      </c>
-      <c r="B60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C60" t="s">
-        <v>123</v>
+      <c r="C60" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EF4A96-354F-EF47-9CA6-64870252A183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFA0F17-B616-C141-8340-014254F50626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="500" windowWidth="27520" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
@@ -393,18 +393,6 @@
     <t>Onshore_Wind, PV, DAC_Adsorption_onshore, HeatPump_AirSourced_onshore</t>
   </si>
   <si>
-    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
-  </si>
-  <si>
-    <t>DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
-  </si>
-  <si>
-    <t>DAC_Adsorption_offshore, HeatPump_AirSourced_offshore, PermanentStorage_CO2_simple</t>
-  </si>
-  <si>
-    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_AirSourced_offshore, PermanentStorage_CO2_simple</t>
-  </si>
-  <si>
     <t>DK_ST1</t>
   </si>
   <si>
@@ -420,7 +408,19 @@
     <t>NO_ST1</t>
   </si>
   <si>
-    <t>PermanentStorage_CO2_simple, DAC_Adsorption_offshore, HeatPump_AirSourced_offshore</t>
+    <t>PermanentStorage_CO2_simple, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced</t>
+  </si>
+  <si>
+    <t>DAC_Adsorption_offshore, HeatPump_SeaWaterSourced</t>
+  </si>
+  <si>
+    <t>DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
   </si>
 </sst>
 </file>
@@ -1191,7 +1191,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>45</v>
@@ -1282,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -1329,7 +1329,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
         <v>45</v>
@@ -1376,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
@@ -1470,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -1517,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
@@ -1564,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -1611,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
@@ -1658,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
@@ -1705,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
@@ -1752,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -1846,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
@@ -3221,7 +3221,7 @@
         <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
         <v>49</v>
@@ -3304,7 +3304,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D41" t="s">
         <v>49</v>
@@ -3387,7 +3387,7 @@
         <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
         <v>49</v>
@@ -3470,7 +3470,7 @@
         <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
         <v>49</v>
@@ -3553,7 +3553,7 @@
         <v>64</v>
       </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
         <v>49</v>
@@ -3636,7 +3636,7 @@
         <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D45" t="s">
         <v>49</v>
@@ -3719,7 +3719,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D46" t="s">
         <v>49</v>
@@ -3802,7 +3802,7 @@
         <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
@@ -3885,7 +3885,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
         <v>49</v>
@@ -3968,7 +3968,7 @@
         <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D49" t="s">
         <v>49</v>
@@ -4051,7 +4051,7 @@
         <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D50" t="s">
         <v>49</v>
@@ -4134,7 +4134,7 @@
         <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D51" t="s">
         <v>49</v>
@@ -4217,7 +4217,7 @@
         <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
         <v>49</v>
@@ -4300,7 +4300,7 @@
         <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D53" t="s">
         <v>49</v>
@@ -4383,7 +4383,7 @@
         <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D54" t="s">
         <v>49</v>
@@ -4466,7 +4466,7 @@
         <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
         <v>49</v>
@@ -4549,7 +4549,7 @@
         <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
         <v>49</v>
@@ -4626,46 +4626,46 @@
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" t="s">
         <v>122</v>
-      </c>
-      <c r="C57" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFA0F17-B616-C141-8340-014254F50626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F23B9AD-F098-4541-B914-5DDB019DD30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
   <sheets>
     <sheet name="NewTechnologies" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="132">
   <si>
     <t>Electrolyser_PEM_offshore</t>
   </si>
@@ -421,6 +421,21 @@
   </si>
   <si>
     <t>Offshore_Wind, DAC_Adsorption_offshore, HeatPump_SeaWaterSourced, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>Offshore_DAC_only</t>
+  </si>
+  <si>
+    <t>Onshore_DAC_only</t>
+  </si>
+  <si>
+    <t>Onshore_DAC_retrofits</t>
+  </si>
+  <si>
+    <t>PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>Offshore_Wind, PermanentStorage_CO2_simple</t>
   </si>
 </sst>
 </file>
@@ -764,24 +779,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA60"/>
+  <dimension ref="A1:AD60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="43" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24" customWidth="1"/>
-    <col min="18" max="18" width="15.33203125" customWidth="1"/>
-    <col min="20" max="20" width="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="15.33203125" customWidth="1"/>
+    <col min="14" max="14" width="43" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="43" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="15.33203125" customWidth="1"/>
+    <col min="23" max="23" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -792,398 +807,407 @@
         <v>74</v>
       </c>
       <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>113</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>114</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>115</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>88</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>89</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>90</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>91</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="T1" t="str">
         <f>C1&amp;"_no_onshore_wind"</f>
         <v>RE_only_no_onshore_wind</v>
       </c>
-      <c r="R1" t="str">
-        <f>D1&amp;"_no_onshore_wind"</f>
-        <v>Battery_on_no_onshore_wind</v>
-      </c>
-      <c r="S1" t="str">
-        <f>E1&amp;"_no_onshore_wind"</f>
-        <v>Battery_off_no_onshore_wind</v>
-      </c>
-      <c r="T1" t="str">
-        <f>F1&amp;"_no_onshore_wind"</f>
-        <v>Battery_all_no_onshore_wind</v>
-      </c>
       <c r="U1" t="str">
         <f>G1&amp;"_no_onshore_wind"</f>
+        <v>Battery_on_no_onshore_wind</v>
+      </c>
+      <c r="V1" t="str">
+        <f>H1&amp;"_no_onshore_wind"</f>
+        <v>Battery_off_no_onshore_wind</v>
+      </c>
+      <c r="W1" t="str">
+        <f>I1&amp;"_no_onshore_wind"</f>
+        <v>Battery_all_no_onshore_wind</v>
+      </c>
+      <c r="X1" t="str">
+        <f>J1&amp;"_no_onshore_wind"</f>
         <v>ElectricityGrid_all_no_onshore_wind</v>
       </c>
-      <c r="V1" t="str">
-        <f t="shared" ref="V1:AA1" si="0">K1&amp;"_no_onshore_wind"</f>
+      <c r="Y1" t="str">
+        <f t="shared" ref="Y1:AD1" si="0">N1&amp;"_no_onshore_wind"</f>
         <v>Hydrogen_Baseline_no_onshore_wind</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Z1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H1_no_onshore_wind</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AA1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H2_no_onshore_wind</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AB1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H3_no_onshore_wind</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AC1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H4_no_onshore_wind</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AD1" t="str">
         <f t="shared" si="0"/>
         <v>All_no_onshore_wind</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
-        <v>0</v>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
-      <c r="P2" t="s">
+      <c r="O2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
         <v>69</v>
       </c>
-      <c r="S2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" t="s">
-        <v>45</v>
-      </c>
       <c r="V2" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y2" t="s">
         <v>0</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="Z2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>0</v>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
       </c>
       <c r="N3" t="s">
         <v>0</v>
       </c>
-      <c r="P3" t="s">
+      <c r="O3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>0</v>
+      </c>
+      <c r="S3" t="s">
         <v>69</v>
       </c>
-      <c r="S3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" t="s">
-        <v>45</v>
-      </c>
       <c r="V3" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y3" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="Z3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" t="s">
-        <v>0</v>
-      </c>
-      <c r="L4" t="s">
-        <v>0</v>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
       </c>
       <c r="N4" t="s">
         <v>0</v>
       </c>
-      <c r="P4" t="s">
+      <c r="O4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
         <v>69</v>
       </c>
-      <c r="S4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" t="s">
-        <v>45</v>
-      </c>
       <c r="V4" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y4" t="s">
         <v>0</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="Z4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>0</v>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
       </c>
       <c r="N5" t="s">
         <v>0</v>
       </c>
-      <c r="P5" t="s">
+      <c r="O5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
         <v>69</v>
       </c>
-      <c r="S5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T5" t="s">
-        <v>45</v>
-      </c>
       <c r="V5" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y5" t="s">
         <v>0</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="Z5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" t="s">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>0</v>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
       </c>
       <c r="N6" t="s">
         <v>0</v>
       </c>
-      <c r="P6" t="s">
+      <c r="O6" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
         <v>69</v>
       </c>
-      <c r="S6" t="s">
-        <v>45</v>
-      </c>
-      <c r="T6" t="s">
-        <v>45</v>
-      </c>
       <c r="V6" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y6" t="s">
         <v>0</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="Z6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" t="s">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>0</v>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
       </c>
       <c r="N7" t="s">
         <v>0</v>
       </c>
-      <c r="P7" t="s">
+      <c r="O7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
         <v>69</v>
       </c>
-      <c r="S7" t="s">
-        <v>45</v>
-      </c>
-      <c r="T7" t="s">
-        <v>45</v>
-      </c>
       <c r="V7" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y7" t="s">
         <v>0</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="Z7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" t="s">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>0</v>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
       </c>
       <c r="N8" t="s">
         <v>0</v>
       </c>
-      <c r="P8" t="s">
+      <c r="O8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
         <v>69</v>
       </c>
-      <c r="S8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T8" t="s">
-        <v>45</v>
-      </c>
       <c r="V8" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W8" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y8" t="s">
         <v>0</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="Z8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1193,88 +1217,97 @@
       <c r="C9" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>0</v>
+      <c r="D9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
       </c>
       <c r="N9" t="s">
         <v>0</v>
       </c>
-      <c r="P9" t="s">
+      <c r="O9" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>0</v>
+      </c>
+      <c r="S9" t="s">
         <v>69</v>
       </c>
-      <c r="S9" t="s">
-        <v>45</v>
-      </c>
-      <c r="T9" t="s">
-        <v>45</v>
-      </c>
       <c r="V9" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W9" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y9" t="s">
         <v>0</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="Z9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" t="s">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>0</v>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
       </c>
       <c r="N10" t="s">
         <v>0</v>
       </c>
-      <c r="P10" t="s">
+      <c r="O10" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>0</v>
+      </c>
+      <c r="S10" t="s">
         <v>69</v>
       </c>
-      <c r="S10" t="s">
-        <v>45</v>
-      </c>
-      <c r="T10" t="s">
-        <v>45</v>
-      </c>
       <c r="V10" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W10" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y10" t="s">
         <v>0</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="Z10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1284,44 +1317,53 @@
       <c r="C11" t="s">
         <v>122</v>
       </c>
+      <c r="D11" t="s">
+        <v>122</v>
+      </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
       </c>
       <c r="N11" t="s">
         <v>0</v>
       </c>
-      <c r="P11" t="s">
+      <c r="O11" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>0</v>
+      </c>
+      <c r="S11" t="s">
         <v>69</v>
       </c>
-      <c r="S11" t="s">
-        <v>45</v>
-      </c>
-      <c r="T11" t="s">
-        <v>45</v>
-      </c>
       <c r="V11" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W11" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y11" t="s">
         <v>0</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="Z11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1331,44 +1373,53 @@
       <c r="C12" t="s">
         <v>122</v>
       </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
       </c>
       <c r="N12" t="s">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
+      <c r="O12" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
         <v>69</v>
       </c>
-      <c r="S12" t="s">
-        <v>45</v>
-      </c>
-      <c r="T12" t="s">
-        <v>45</v>
-      </c>
       <c r="V12" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W12" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y12" t="s">
         <v>0</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="Z12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1378,44 +1429,53 @@
       <c r="C13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" t="s">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>0</v>
+      <c r="D13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
       </c>
       <c r="N13" t="s">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
+      <c r="O13" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>0</v>
+      </c>
+      <c r="S13" t="s">
         <v>69</v>
       </c>
-      <c r="S13" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" t="s">
-        <v>45</v>
-      </c>
       <c r="V13" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W13" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y13" t="s">
         <v>0</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="Z13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1425,44 +1485,47 @@
       <c r="C14" t="s">
         <v>123</v>
       </c>
-      <c r="E14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" t="s">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>0</v>
+      <c r="D14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
       </c>
       <c r="N14" t="s">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
+      <c r="O14" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
         <v>69</v>
       </c>
-      <c r="S14" t="s">
-        <v>45</v>
-      </c>
-      <c r="T14" t="s">
-        <v>45</v>
-      </c>
       <c r="V14" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W14" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y14" t="s">
         <v>0</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="Z14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1472,44 +1535,47 @@
       <c r="C15" t="s">
         <v>123</v>
       </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" t="s">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>0</v>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
       </c>
       <c r="N15" t="s">
         <v>0</v>
       </c>
-      <c r="P15" t="s">
+      <c r="O15" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>0</v>
+      </c>
+      <c r="S15" t="s">
         <v>69</v>
       </c>
-      <c r="S15" t="s">
-        <v>45</v>
-      </c>
-      <c r="T15" t="s">
-        <v>45</v>
-      </c>
       <c r="V15" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W15" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y15" t="s">
         <v>0</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="Z15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1519,44 +1585,47 @@
       <c r="C16" t="s">
         <v>123</v>
       </c>
-      <c r="E16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-      <c r="K16" t="s">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>0</v>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
       </c>
       <c r="N16" t="s">
         <v>0</v>
       </c>
-      <c r="P16" t="s">
+      <c r="O16" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>0</v>
+      </c>
+      <c r="S16" t="s">
         <v>69</v>
       </c>
-      <c r="S16" t="s">
-        <v>45</v>
-      </c>
-      <c r="T16" t="s">
-        <v>45</v>
-      </c>
       <c r="V16" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W16" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y16" t="s">
         <v>0</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="Z16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1566,44 +1635,47 @@
       <c r="C17" t="s">
         <v>123</v>
       </c>
-      <c r="E17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" t="s">
-        <v>45</v>
-      </c>
-      <c r="K17" t="s">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>0</v>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
       </c>
       <c r="N17" t="s">
         <v>0</v>
       </c>
-      <c r="P17" t="s">
+      <c r="O17" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>0</v>
+      </c>
+      <c r="S17" t="s">
         <v>69</v>
       </c>
-      <c r="S17" t="s">
-        <v>45</v>
-      </c>
-      <c r="T17" t="s">
-        <v>45</v>
-      </c>
       <c r="V17" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W17" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y17" t="s">
         <v>0</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="Z17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1613,44 +1685,47 @@
       <c r="C18" t="s">
         <v>123</v>
       </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" t="s">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>0</v>
+      <c r="D18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
       </c>
       <c r="N18" t="s">
         <v>0</v>
       </c>
-      <c r="P18" t="s">
+      <c r="O18" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>0</v>
+      </c>
+      <c r="S18" t="s">
         <v>69</v>
       </c>
-      <c r="S18" t="s">
-        <v>45</v>
-      </c>
-      <c r="T18" t="s">
-        <v>45</v>
-      </c>
       <c r="V18" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W18" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y18" t="s">
         <v>0</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="Z18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1660,44 +1735,47 @@
       <c r="C19" t="s">
         <v>123</v>
       </c>
-      <c r="E19" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" t="s">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>0</v>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
       </c>
       <c r="N19" t="s">
         <v>0</v>
       </c>
-      <c r="P19" t="s">
+      <c r="O19" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>0</v>
+      </c>
+      <c r="S19" t="s">
         <v>69</v>
       </c>
-      <c r="S19" t="s">
-        <v>45</v>
-      </c>
-      <c r="T19" t="s">
-        <v>45</v>
-      </c>
       <c r="V19" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W19" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y19" t="s">
         <v>0</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="Z19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1707,44 +1785,53 @@
       <c r="C20" t="s">
         <v>124</v>
       </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" t="s">
-        <v>0</v>
-      </c>
-      <c r="L20" t="s">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="H20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" t="s">
+        <v>45</v>
       </c>
       <c r="N20" t="s">
         <v>0</v>
       </c>
-      <c r="P20" t="s">
+      <c r="O20" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>0</v>
+      </c>
+      <c r="S20" t="s">
         <v>69</v>
       </c>
-      <c r="S20" t="s">
-        <v>45</v>
-      </c>
-      <c r="T20" t="s">
-        <v>45</v>
-      </c>
       <c r="V20" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W20" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y20" t="s">
         <v>0</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="Z20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1754,44 +1841,53 @@
       <c r="C21" t="s">
         <v>124</v>
       </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="F21" t="s">
-        <v>45</v>
-      </c>
-      <c r="K21" t="s">
-        <v>0</v>
-      </c>
-      <c r="L21" t="s">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="H21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
       </c>
       <c r="N21" t="s">
         <v>0</v>
       </c>
-      <c r="P21" t="s">
+      <c r="O21" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>0</v>
+      </c>
+      <c r="S21" t="s">
         <v>69</v>
       </c>
-      <c r="S21" t="s">
-        <v>45</v>
-      </c>
-      <c r="T21" t="s">
-        <v>45</v>
-      </c>
       <c r="V21" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W21" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y21" t="s">
         <v>0</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="Z21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1801,44 +1897,47 @@
       <c r="C22" t="s">
         <v>123</v>
       </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" t="s">
-        <v>0</v>
-      </c>
-      <c r="L22" t="s">
-        <v>0</v>
+      <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
       </c>
       <c r="N22" t="s">
         <v>0</v>
       </c>
-      <c r="P22" t="s">
+      <c r="O22" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>0</v>
+      </c>
+      <c r="S22" t="s">
         <v>69</v>
       </c>
-      <c r="S22" t="s">
-        <v>45</v>
-      </c>
-      <c r="T22" t="s">
-        <v>45</v>
-      </c>
       <c r="V22" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W22" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y22" t="s">
         <v>0</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="Z22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1848,44 +1947,53 @@
       <c r="C23" t="s">
         <v>124</v>
       </c>
+      <c r="D23" t="s">
+        <v>124</v>
+      </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
-      </c>
-      <c r="K23" t="s">
-        <v>0</v>
-      </c>
-      <c r="L23" t="s">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="H23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" t="s">
+        <v>45</v>
       </c>
       <c r="N23" t="s">
         <v>0</v>
       </c>
-      <c r="P23" t="s">
+      <c r="O23" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>0</v>
+      </c>
+      <c r="S23" t="s">
         <v>69</v>
       </c>
-      <c r="S23" t="s">
-        <v>45</v>
-      </c>
-      <c r="T23" t="s">
-        <v>45</v>
-      </c>
       <c r="V23" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W23" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y23" t="s">
         <v>0</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="Z23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1896,79 +2004,88 @@
         <v>116</v>
       </c>
       <c r="D24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" t="s">
         <v>70</v>
       </c>
-      <c r="E24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" t="s">
         <v>70</v>
       </c>
-      <c r="G24" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" t="s">
-        <v>65</v>
-      </c>
-      <c r="I24" t="s">
-        <v>65</v>
-      </c>
       <c r="J24" t="s">
         <v>65</v>
       </c>
       <c r="K24" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" t="s">
+        <v>65</v>
+      </c>
+      <c r="N24" t="s">
         <v>71</v>
       </c>
-      <c r="L24" t="s">
+      <c r="O24" t="s">
         <v>92</v>
       </c>
-      <c r="M24" t="s">
+      <c r="P24" t="s">
         <v>71</v>
       </c>
-      <c r="N24" t="s">
+      <c r="Q24" t="s">
         <v>93</v>
       </c>
-      <c r="O24" t="s">
+      <c r="R24" t="s">
         <v>71</v>
       </c>
-      <c r="P24" t="s">
+      <c r="S24" t="s">
         <v>72</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="T24" t="s">
         <v>83</v>
       </c>
-      <c r="R24" t="s">
+      <c r="U24" t="s">
         <v>84</v>
       </c>
-      <c r="S24" t="s">
+      <c r="V24" t="s">
         <v>83</v>
       </c>
-      <c r="T24" t="s">
+      <c r="W24" t="s">
         <v>84</v>
       </c>
-      <c r="U24" t="s">
+      <c r="X24" t="s">
         <v>83</v>
       </c>
-      <c r="V24" t="s">
+      <c r="Y24" t="s">
         <v>85</v>
       </c>
-      <c r="W24" t="s">
+      <c r="Z24" t="s">
         <v>94</v>
       </c>
-      <c r="X24" t="s">
+      <c r="AA24" t="s">
         <v>85</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AB24" t="s">
         <v>95</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AC24" t="s">
         <v>85</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AD24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1979,79 +2096,88 @@
         <v>116</v>
       </c>
       <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" t="s">
         <v>70</v>
       </c>
-      <c r="E25" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I25" t="s">
         <v>70</v>
       </c>
-      <c r="G25" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" t="s">
-        <v>65</v>
-      </c>
-      <c r="I25" t="s">
-        <v>65</v>
-      </c>
       <c r="J25" t="s">
         <v>65</v>
       </c>
       <c r="K25" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" t="s">
+        <v>65</v>
+      </c>
+      <c r="N25" t="s">
         <v>71</v>
       </c>
-      <c r="L25" t="s">
+      <c r="O25" t="s">
         <v>92</v>
       </c>
-      <c r="M25" t="s">
+      <c r="P25" t="s">
         <v>71</v>
       </c>
-      <c r="N25" t="s">
+      <c r="Q25" t="s">
         <v>93</v>
       </c>
-      <c r="O25" t="s">
+      <c r="R25" t="s">
         <v>71</v>
       </c>
-      <c r="P25" t="s">
+      <c r="S25" t="s">
         <v>72</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="T25" t="s">
         <v>83</v>
       </c>
-      <c r="R25" t="s">
+      <c r="U25" t="s">
         <v>84</v>
       </c>
-      <c r="S25" t="s">
+      <c r="V25" t="s">
         <v>83</v>
       </c>
-      <c r="T25" t="s">
+      <c r="W25" t="s">
         <v>84</v>
       </c>
-      <c r="U25" t="s">
+      <c r="X25" t="s">
         <v>83</v>
       </c>
-      <c r="V25" t="s">
+      <c r="Y25" t="s">
         <v>85</v>
       </c>
-      <c r="W25" t="s">
+      <c r="Z25" t="s">
         <v>94</v>
       </c>
-      <c r="X25" t="s">
+      <c r="AA25" t="s">
         <v>85</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="AB25" t="s">
         <v>95</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AC25" t="s">
         <v>85</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AD25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -2062,79 +2188,88 @@
         <v>116</v>
       </c>
       <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" t="s">
         <v>70</v>
       </c>
-      <c r="E26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26" t="s">
         <v>70</v>
       </c>
-      <c r="G26" t="s">
-        <v>65</v>
-      </c>
-      <c r="H26" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26" t="s">
-        <v>65</v>
-      </c>
       <c r="J26" t="s">
         <v>65</v>
       </c>
       <c r="K26" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" t="s">
+        <v>65</v>
+      </c>
+      <c r="N26" t="s">
         <v>71</v>
       </c>
-      <c r="L26" t="s">
+      <c r="O26" t="s">
         <v>92</v>
       </c>
-      <c r="M26" t="s">
+      <c r="P26" t="s">
         <v>71</v>
       </c>
-      <c r="N26" t="s">
+      <c r="Q26" t="s">
         <v>93</v>
       </c>
-      <c r="O26" t="s">
+      <c r="R26" t="s">
         <v>71</v>
       </c>
-      <c r="P26" t="s">
+      <c r="S26" t="s">
         <v>72</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="T26" t="s">
         <v>83</v>
       </c>
-      <c r="R26" t="s">
+      <c r="U26" t="s">
         <v>84</v>
       </c>
-      <c r="S26" t="s">
+      <c r="V26" t="s">
         <v>83</v>
       </c>
-      <c r="T26" t="s">
+      <c r="W26" t="s">
         <v>84</v>
       </c>
-      <c r="U26" t="s">
+      <c r="X26" t="s">
         <v>83</v>
       </c>
-      <c r="V26" t="s">
+      <c r="Y26" t="s">
         <v>85</v>
       </c>
-      <c r="W26" t="s">
+      <c r="Z26" t="s">
         <v>94</v>
       </c>
-      <c r="X26" t="s">
+      <c r="AA26" t="s">
         <v>85</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AB26" t="s">
         <v>95</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AC26" t="s">
         <v>85</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AD26" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2145,79 +2280,88 @@
         <v>116</v>
       </c>
       <c r="D27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
         <v>70</v>
       </c>
-      <c r="E27" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="H27" t="s">
+        <v>65</v>
+      </c>
+      <c r="I27" t="s">
         <v>70</v>
       </c>
-      <c r="G27" t="s">
-        <v>65</v>
-      </c>
-      <c r="H27" t="s">
-        <v>65</v>
-      </c>
-      <c r="I27" t="s">
-        <v>65</v>
-      </c>
       <c r="J27" t="s">
         <v>65</v>
       </c>
       <c r="K27" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" t="s">
+        <v>65</v>
+      </c>
+      <c r="N27" t="s">
         <v>71</v>
       </c>
-      <c r="L27" t="s">
+      <c r="O27" t="s">
         <v>92</v>
       </c>
-      <c r="M27" t="s">
+      <c r="P27" t="s">
         <v>71</v>
       </c>
-      <c r="N27" t="s">
+      <c r="Q27" t="s">
         <v>93</v>
       </c>
-      <c r="O27" t="s">
+      <c r="R27" t="s">
         <v>71</v>
       </c>
-      <c r="P27" t="s">
+      <c r="S27" t="s">
         <v>72</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="T27" t="s">
         <v>83</v>
       </c>
-      <c r="R27" t="s">
+      <c r="U27" t="s">
         <v>84</v>
       </c>
-      <c r="S27" t="s">
+      <c r="V27" t="s">
         <v>83</v>
       </c>
-      <c r="T27" t="s">
+      <c r="W27" t="s">
         <v>84</v>
       </c>
-      <c r="U27" t="s">
+      <c r="X27" t="s">
         <v>83</v>
       </c>
-      <c r="V27" t="s">
+      <c r="Y27" t="s">
         <v>85</v>
       </c>
-      <c r="W27" t="s">
+      <c r="Z27" t="s">
         <v>94</v>
       </c>
-      <c r="X27" t="s">
+      <c r="AA27" t="s">
         <v>85</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="AB27" t="s">
         <v>95</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AC27" t="s">
         <v>85</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AD27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -2228,79 +2372,88 @@
         <v>116</v>
       </c>
       <c r="D28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" t="s">
         <v>70</v>
       </c>
-      <c r="E28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
+        <v>65</v>
+      </c>
+      <c r="I28" t="s">
         <v>70</v>
       </c>
-      <c r="G28" t="s">
-        <v>65</v>
-      </c>
-      <c r="H28" t="s">
-        <v>65</v>
-      </c>
-      <c r="I28" t="s">
-        <v>65</v>
-      </c>
       <c r="J28" t="s">
         <v>65</v>
       </c>
       <c r="K28" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" t="s">
+        <v>65</v>
+      </c>
+      <c r="N28" t="s">
         <v>71</v>
       </c>
-      <c r="L28" t="s">
+      <c r="O28" t="s">
         <v>92</v>
       </c>
-      <c r="M28" t="s">
+      <c r="P28" t="s">
         <v>71</v>
       </c>
-      <c r="N28" t="s">
+      <c r="Q28" t="s">
         <v>93</v>
       </c>
-      <c r="O28" t="s">
+      <c r="R28" t="s">
         <v>71</v>
       </c>
-      <c r="P28" t="s">
+      <c r="S28" t="s">
         <v>72</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="T28" t="s">
         <v>83</v>
       </c>
-      <c r="R28" t="s">
+      <c r="U28" t="s">
         <v>84</v>
       </c>
-      <c r="S28" t="s">
+      <c r="V28" t="s">
         <v>83</v>
       </c>
-      <c r="T28" t="s">
+      <c r="W28" t="s">
         <v>84</v>
       </c>
-      <c r="U28" t="s">
+      <c r="X28" t="s">
         <v>83</v>
       </c>
-      <c r="V28" t="s">
+      <c r="Y28" t="s">
         <v>85</v>
       </c>
-      <c r="W28" t="s">
+      <c r="Z28" t="s">
         <v>94</v>
       </c>
-      <c r="X28" t="s">
+      <c r="AA28" t="s">
         <v>85</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="AB28" t="s">
         <v>95</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AC28" t="s">
         <v>85</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AD28" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -2311,79 +2464,88 @@
         <v>116</v>
       </c>
       <c r="D29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" t="s">
         <v>70</v>
       </c>
-      <c r="E29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
+        <v>65</v>
+      </c>
+      <c r="I29" t="s">
         <v>70</v>
       </c>
-      <c r="G29" t="s">
-        <v>65</v>
-      </c>
-      <c r="H29" t="s">
-        <v>65</v>
-      </c>
-      <c r="I29" t="s">
-        <v>65</v>
-      </c>
       <c r="J29" t="s">
         <v>65</v>
       </c>
       <c r="K29" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" t="s">
         <v>71</v>
       </c>
-      <c r="L29" t="s">
+      <c r="O29" t="s">
         <v>92</v>
       </c>
-      <c r="M29" t="s">
+      <c r="P29" t="s">
         <v>71</v>
       </c>
-      <c r="N29" t="s">
+      <c r="Q29" t="s">
         <v>93</v>
       </c>
-      <c r="O29" t="s">
+      <c r="R29" t="s">
         <v>71</v>
       </c>
-      <c r="P29" t="s">
+      <c r="S29" t="s">
         <v>72</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="T29" t="s">
         <v>83</v>
       </c>
-      <c r="R29" t="s">
+      <c r="U29" t="s">
         <v>84</v>
       </c>
-      <c r="S29" t="s">
+      <c r="V29" t="s">
         <v>83</v>
       </c>
-      <c r="T29" t="s">
+      <c r="W29" t="s">
         <v>84</v>
       </c>
-      <c r="U29" t="s">
+      <c r="X29" t="s">
         <v>83</v>
       </c>
-      <c r="V29" t="s">
+      <c r="Y29" t="s">
         <v>85</v>
       </c>
-      <c r="W29" t="s">
+      <c r="Z29" t="s">
         <v>94</v>
       </c>
-      <c r="X29" t="s">
+      <c r="AA29" t="s">
         <v>85</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="AB29" t="s">
         <v>95</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AC29" t="s">
         <v>85</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AD29" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -2394,79 +2556,88 @@
         <v>116</v>
       </c>
       <c r="D30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" t="s">
         <v>70</v>
       </c>
-      <c r="E30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" t="s">
         <v>70</v>
       </c>
-      <c r="G30" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30" t="s">
-        <v>65</v>
-      </c>
       <c r="J30" t="s">
         <v>65</v>
       </c>
       <c r="K30" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" t="s">
         <v>71</v>
       </c>
-      <c r="L30" t="s">
+      <c r="O30" t="s">
         <v>92</v>
       </c>
-      <c r="M30" t="s">
+      <c r="P30" t="s">
         <v>71</v>
       </c>
-      <c r="N30" t="s">
+      <c r="Q30" t="s">
         <v>93</v>
       </c>
-      <c r="O30" t="s">
+      <c r="R30" t="s">
         <v>71</v>
       </c>
-      <c r="P30" t="s">
+      <c r="S30" t="s">
         <v>72</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="T30" t="s">
         <v>83</v>
       </c>
-      <c r="R30" t="s">
+      <c r="U30" t="s">
         <v>84</v>
       </c>
-      <c r="S30" t="s">
+      <c r="V30" t="s">
         <v>83</v>
       </c>
-      <c r="T30" t="s">
+      <c r="W30" t="s">
         <v>84</v>
       </c>
-      <c r="U30" t="s">
+      <c r="X30" t="s">
         <v>83</v>
       </c>
-      <c r="V30" t="s">
+      <c r="Y30" t="s">
         <v>85</v>
       </c>
-      <c r="W30" t="s">
+      <c r="Z30" t="s">
         <v>94</v>
       </c>
-      <c r="X30" t="s">
+      <c r="AA30" t="s">
         <v>85</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="AB30" t="s">
         <v>95</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AC30" t="s">
         <v>85</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AD30" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2477,79 +2648,88 @@
         <v>116</v>
       </c>
       <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" t="s">
         <v>70</v>
       </c>
-      <c r="E31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" t="s">
         <v>70</v>
       </c>
-      <c r="G31" t="s">
-        <v>65</v>
-      </c>
-      <c r="H31" t="s">
-        <v>65</v>
-      </c>
-      <c r="I31" t="s">
-        <v>65</v>
-      </c>
       <c r="J31" t="s">
         <v>65</v>
       </c>
       <c r="K31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" t="s">
         <v>71</v>
       </c>
-      <c r="L31" t="s">
+      <c r="O31" t="s">
         <v>92</v>
       </c>
-      <c r="M31" t="s">
+      <c r="P31" t="s">
         <v>71</v>
       </c>
-      <c r="N31" t="s">
+      <c r="Q31" t="s">
         <v>93</v>
       </c>
-      <c r="O31" t="s">
+      <c r="R31" t="s">
         <v>71</v>
       </c>
-      <c r="P31" t="s">
+      <c r="S31" t="s">
         <v>72</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="T31" t="s">
         <v>83</v>
       </c>
-      <c r="R31" t="s">
+      <c r="U31" t="s">
         <v>84</v>
       </c>
-      <c r="S31" t="s">
+      <c r="V31" t="s">
         <v>83</v>
       </c>
-      <c r="T31" t="s">
+      <c r="W31" t="s">
         <v>84</v>
       </c>
-      <c r="U31" t="s">
+      <c r="X31" t="s">
         <v>83</v>
       </c>
-      <c r="V31" t="s">
+      <c r="Y31" t="s">
         <v>85</v>
       </c>
-      <c r="W31" t="s">
+      <c r="Z31" t="s">
         <v>94</v>
       </c>
-      <c r="X31" t="s">
+      <c r="AA31" t="s">
         <v>85</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="AB31" t="s">
         <v>95</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AC31" t="s">
         <v>85</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AD31" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2560,79 +2740,88 @@
         <v>116</v>
       </c>
       <c r="D32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" t="s">
         <v>70</v>
       </c>
-      <c r="E32" t="s">
-        <v>65</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" t="s">
         <v>70</v>
       </c>
-      <c r="G32" t="s">
-        <v>65</v>
-      </c>
-      <c r="H32" t="s">
-        <v>65</v>
-      </c>
-      <c r="I32" t="s">
-        <v>65</v>
-      </c>
       <c r="J32" t="s">
         <v>65</v>
       </c>
       <c r="K32" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" t="s">
         <v>71</v>
       </c>
-      <c r="L32" t="s">
+      <c r="O32" t="s">
         <v>92</v>
       </c>
-      <c r="M32" t="s">
+      <c r="P32" t="s">
         <v>71</v>
       </c>
-      <c r="N32" t="s">
+      <c r="Q32" t="s">
         <v>93</v>
       </c>
-      <c r="O32" t="s">
+      <c r="R32" t="s">
         <v>71</v>
       </c>
-      <c r="P32" t="s">
+      <c r="S32" t="s">
         <v>72</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="T32" t="s">
         <v>83</v>
       </c>
-      <c r="R32" t="s">
+      <c r="U32" t="s">
         <v>84</v>
       </c>
-      <c r="S32" t="s">
+      <c r="V32" t="s">
         <v>83</v>
       </c>
-      <c r="T32" t="s">
+      <c r="W32" t="s">
         <v>84</v>
       </c>
-      <c r="U32" t="s">
+      <c r="X32" t="s">
         <v>83</v>
       </c>
-      <c r="V32" t="s">
+      <c r="Y32" t="s">
         <v>85</v>
       </c>
-      <c r="W32" t="s">
+      <c r="Z32" t="s">
         <v>94</v>
       </c>
-      <c r="X32" t="s">
+      <c r="AA32" t="s">
         <v>85</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="AB32" t="s">
         <v>95</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AC32" t="s">
         <v>85</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AD32" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2643,79 +2832,88 @@
         <v>116</v>
       </c>
       <c r="D33" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" t="s">
         <v>70</v>
       </c>
-      <c r="E33" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" t="s">
         <v>70</v>
       </c>
-      <c r="G33" t="s">
-        <v>65</v>
-      </c>
-      <c r="H33" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33" t="s">
-        <v>65</v>
-      </c>
       <c r="J33" t="s">
         <v>65</v>
       </c>
       <c r="K33" t="s">
+        <v>65</v>
+      </c>
+      <c r="L33" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" t="s">
+        <v>65</v>
+      </c>
+      <c r="N33" t="s">
         <v>71</v>
       </c>
-      <c r="L33" t="s">
+      <c r="O33" t="s">
         <v>92</v>
       </c>
-      <c r="M33" t="s">
+      <c r="P33" t="s">
         <v>71</v>
       </c>
-      <c r="N33" t="s">
+      <c r="Q33" t="s">
         <v>93</v>
       </c>
-      <c r="O33" t="s">
+      <c r="R33" t="s">
         <v>71</v>
       </c>
-      <c r="P33" t="s">
+      <c r="S33" t="s">
         <v>72</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="T33" t="s">
         <v>83</v>
       </c>
-      <c r="R33" t="s">
+      <c r="U33" t="s">
         <v>84</v>
       </c>
-      <c r="S33" t="s">
+      <c r="V33" t="s">
         <v>83</v>
       </c>
-      <c r="T33" t="s">
+      <c r="W33" t="s">
         <v>84</v>
       </c>
-      <c r="U33" t="s">
+      <c r="X33" t="s">
         <v>83</v>
       </c>
-      <c r="V33" t="s">
+      <c r="Y33" t="s">
         <v>85</v>
       </c>
-      <c r="W33" t="s">
+      <c r="Z33" t="s">
         <v>94</v>
       </c>
-      <c r="X33" t="s">
+      <c r="AA33" t="s">
         <v>85</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="AB33" t="s">
         <v>95</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AC33" t="s">
         <v>85</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AD33" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2726,79 +2924,88 @@
         <v>116</v>
       </c>
       <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" t="s">
         <v>70</v>
       </c>
-      <c r="E34" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="H34" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" t="s">
         <v>70</v>
       </c>
-      <c r="G34" t="s">
-        <v>65</v>
-      </c>
-      <c r="H34" t="s">
-        <v>65</v>
-      </c>
-      <c r="I34" t="s">
-        <v>65</v>
-      </c>
       <c r="J34" t="s">
         <v>65</v>
       </c>
       <c r="K34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" t="s">
+        <v>65</v>
+      </c>
+      <c r="N34" t="s">
         <v>71</v>
       </c>
-      <c r="L34" t="s">
+      <c r="O34" t="s">
         <v>92</v>
       </c>
-      <c r="M34" t="s">
+      <c r="P34" t="s">
         <v>71</v>
       </c>
-      <c r="N34" t="s">
+      <c r="Q34" t="s">
         <v>93</v>
       </c>
-      <c r="O34" t="s">
+      <c r="R34" t="s">
         <v>71</v>
       </c>
-      <c r="P34" t="s">
+      <c r="S34" t="s">
         <v>72</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="T34" t="s">
         <v>83</v>
       </c>
-      <c r="R34" t="s">
+      <c r="U34" t="s">
         <v>84</v>
       </c>
-      <c r="S34" t="s">
+      <c r="V34" t="s">
         <v>83</v>
       </c>
-      <c r="T34" t="s">
+      <c r="W34" t="s">
         <v>84</v>
       </c>
-      <c r="U34" t="s">
+      <c r="X34" t="s">
         <v>83</v>
       </c>
-      <c r="V34" t="s">
+      <c r="Y34" t="s">
         <v>85</v>
       </c>
-      <c r="W34" t="s">
+      <c r="Z34" t="s">
         <v>94</v>
       </c>
-      <c r="X34" t="s">
+      <c r="AA34" t="s">
         <v>85</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="AB34" t="s">
         <v>95</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AC34" t="s">
         <v>85</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AD34" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2809,79 +3016,88 @@
         <v>116</v>
       </c>
       <c r="D35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" t="s">
         <v>70</v>
       </c>
-      <c r="E35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" t="s">
         <v>70</v>
       </c>
-      <c r="G35" t="s">
-        <v>65</v>
-      </c>
-      <c r="H35" t="s">
-        <v>65</v>
-      </c>
-      <c r="I35" t="s">
-        <v>65</v>
-      </c>
       <c r="J35" t="s">
         <v>65</v>
       </c>
       <c r="K35" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" t="s">
+        <v>65</v>
+      </c>
+      <c r="N35" t="s">
         <v>71</v>
       </c>
-      <c r="L35" t="s">
+      <c r="O35" t="s">
         <v>92</v>
       </c>
-      <c r="M35" t="s">
+      <c r="P35" t="s">
         <v>71</v>
       </c>
-      <c r="N35" t="s">
+      <c r="Q35" t="s">
         <v>93</v>
       </c>
-      <c r="O35" t="s">
+      <c r="R35" t="s">
         <v>71</v>
       </c>
-      <c r="P35" t="s">
+      <c r="S35" t="s">
         <v>72</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="T35" t="s">
         <v>83</v>
       </c>
-      <c r="R35" t="s">
+      <c r="U35" t="s">
         <v>84</v>
       </c>
-      <c r="S35" t="s">
+      <c r="V35" t="s">
         <v>83</v>
       </c>
-      <c r="T35" t="s">
+      <c r="W35" t="s">
         <v>84</v>
       </c>
-      <c r="U35" t="s">
+      <c r="X35" t="s">
         <v>83</v>
       </c>
-      <c r="V35" t="s">
+      <c r="Y35" t="s">
         <v>85</v>
       </c>
-      <c r="W35" t="s">
+      <c r="Z35" t="s">
         <v>94</v>
       </c>
-      <c r="X35" t="s">
+      <c r="AA35" t="s">
         <v>85</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="AB35" t="s">
         <v>95</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AC35" t="s">
         <v>85</v>
       </c>
-      <c r="AA35" t="s">
+      <c r="AD35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -2892,79 +3108,88 @@
         <v>116</v>
       </c>
       <c r="D36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" t="s">
         <v>70</v>
       </c>
-      <c r="E36" t="s">
-        <v>65</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" t="s">
         <v>70</v>
       </c>
-      <c r="G36" t="s">
-        <v>65</v>
-      </c>
-      <c r="H36" t="s">
-        <v>65</v>
-      </c>
-      <c r="I36" t="s">
-        <v>65</v>
-      </c>
       <c r="J36" t="s">
         <v>65</v>
       </c>
       <c r="K36" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" t="s">
+        <v>65</v>
+      </c>
+      <c r="N36" t="s">
         <v>71</v>
       </c>
-      <c r="L36" t="s">
+      <c r="O36" t="s">
         <v>92</v>
       </c>
-      <c r="M36" t="s">
+      <c r="P36" t="s">
         <v>71</v>
       </c>
-      <c r="N36" t="s">
+      <c r="Q36" t="s">
         <v>93</v>
       </c>
-      <c r="O36" t="s">
+      <c r="R36" t="s">
         <v>71</v>
       </c>
-      <c r="P36" t="s">
+      <c r="S36" t="s">
         <v>72</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="T36" t="s">
         <v>83</v>
       </c>
-      <c r="R36" t="s">
+      <c r="U36" t="s">
         <v>84</v>
       </c>
-      <c r="S36" t="s">
+      <c r="V36" t="s">
         <v>83</v>
       </c>
-      <c r="T36" t="s">
+      <c r="W36" t="s">
         <v>84</v>
       </c>
-      <c r="U36" t="s">
+      <c r="X36" t="s">
         <v>83</v>
       </c>
-      <c r="V36" t="s">
+      <c r="Y36" t="s">
         <v>85</v>
       </c>
-      <c r="W36" t="s">
+      <c r="Z36" t="s">
         <v>94</v>
       </c>
-      <c r="X36" t="s">
+      <c r="AA36" t="s">
         <v>85</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="AB36" t="s">
         <v>95</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AC36" t="s">
         <v>85</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AD36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2975,79 +3200,88 @@
         <v>116</v>
       </c>
       <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" t="s">
         <v>70</v>
       </c>
-      <c r="E37" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" t="s">
         <v>70</v>
       </c>
-      <c r="G37" t="s">
-        <v>65</v>
-      </c>
-      <c r="H37" t="s">
-        <v>65</v>
-      </c>
-      <c r="I37" t="s">
-        <v>65</v>
-      </c>
       <c r="J37" t="s">
         <v>65</v>
       </c>
       <c r="K37" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" t="s">
         <v>71</v>
       </c>
-      <c r="L37" t="s">
+      <c r="O37" t="s">
         <v>92</v>
       </c>
-      <c r="M37" t="s">
+      <c r="P37" t="s">
         <v>71</v>
       </c>
-      <c r="N37" t="s">
+      <c r="Q37" t="s">
         <v>93</v>
       </c>
-      <c r="O37" t="s">
+      <c r="R37" t="s">
         <v>71</v>
       </c>
-      <c r="P37" t="s">
+      <c r="S37" t="s">
         <v>72</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="T37" t="s">
         <v>83</v>
       </c>
-      <c r="R37" t="s">
+      <c r="U37" t="s">
         <v>84</v>
       </c>
-      <c r="S37" t="s">
+      <c r="V37" t="s">
         <v>83</v>
       </c>
-      <c r="T37" t="s">
+      <c r="W37" t="s">
         <v>84</v>
       </c>
-      <c r="U37" t="s">
+      <c r="X37" t="s">
         <v>83</v>
       </c>
-      <c r="V37" t="s">
+      <c r="Y37" t="s">
         <v>85</v>
       </c>
-      <c r="W37" t="s">
+      <c r="Z37" t="s">
         <v>94</v>
       </c>
-      <c r="X37" t="s">
+      <c r="AA37" t="s">
         <v>85</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="AB37" t="s">
         <v>95</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AC37" t="s">
         <v>85</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AD37" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -3058,79 +3292,88 @@
         <v>116</v>
       </c>
       <c r="D38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" t="s">
+        <v>116</v>
+      </c>
+      <c r="G38" t="s">
         <v>70</v>
       </c>
-      <c r="E38" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" t="s">
         <v>70</v>
       </c>
-      <c r="G38" t="s">
-        <v>65</v>
-      </c>
-      <c r="H38" t="s">
-        <v>65</v>
-      </c>
-      <c r="I38" t="s">
-        <v>65</v>
-      </c>
       <c r="J38" t="s">
         <v>65</v>
       </c>
       <c r="K38" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" t="s">
+        <v>65</v>
+      </c>
+      <c r="N38" t="s">
         <v>71</v>
       </c>
-      <c r="L38" t="s">
+      <c r="O38" t="s">
         <v>92</v>
       </c>
-      <c r="M38" t="s">
+      <c r="P38" t="s">
         <v>71</v>
       </c>
-      <c r="N38" t="s">
+      <c r="Q38" t="s">
         <v>93</v>
       </c>
-      <c r="O38" t="s">
+      <c r="R38" t="s">
         <v>71</v>
       </c>
-      <c r="P38" t="s">
+      <c r="S38" t="s">
         <v>72</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="T38" t="s">
         <v>83</v>
       </c>
-      <c r="R38" t="s">
+      <c r="U38" t="s">
         <v>84</v>
       </c>
-      <c r="S38" t="s">
+      <c r="V38" t="s">
         <v>83</v>
       </c>
-      <c r="T38" t="s">
+      <c r="W38" t="s">
         <v>84</v>
       </c>
-      <c r="U38" t="s">
+      <c r="X38" t="s">
         <v>83</v>
       </c>
-      <c r="V38" t="s">
+      <c r="Y38" t="s">
         <v>85</v>
       </c>
-      <c r="W38" t="s">
+      <c r="Z38" t="s">
         <v>94</v>
       </c>
-      <c r="X38" t="s">
+      <c r="AA38" t="s">
         <v>85</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="AB38" t="s">
         <v>95</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AC38" t="s">
         <v>85</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AD38" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -3141,79 +3384,88 @@
         <v>116</v>
       </c>
       <c r="D39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" t="s">
         <v>70</v>
       </c>
-      <c r="E39" t="s">
-        <v>65</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="H39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I39" t="s">
         <v>70</v>
       </c>
-      <c r="G39" t="s">
-        <v>65</v>
-      </c>
-      <c r="H39" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39" t="s">
-        <v>65</v>
-      </c>
       <c r="J39" t="s">
         <v>65</v>
       </c>
       <c r="K39" t="s">
+        <v>65</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" t="s">
+        <v>65</v>
+      </c>
+      <c r="N39" t="s">
         <v>71</v>
       </c>
-      <c r="L39" t="s">
+      <c r="O39" t="s">
         <v>92</v>
       </c>
-      <c r="M39" t="s">
+      <c r="P39" t="s">
         <v>71</v>
       </c>
-      <c r="N39" t="s">
+      <c r="Q39" t="s">
         <v>93</v>
       </c>
-      <c r="O39" t="s">
+      <c r="R39" t="s">
         <v>71</v>
       </c>
-      <c r="P39" t="s">
+      <c r="S39" t="s">
         <v>72</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="T39" t="s">
         <v>83</v>
       </c>
-      <c r="R39" t="s">
+      <c r="U39" t="s">
         <v>84</v>
       </c>
-      <c r="S39" t="s">
+      <c r="V39" t="s">
         <v>83</v>
       </c>
-      <c r="T39" t="s">
+      <c r="W39" t="s">
         <v>84</v>
       </c>
-      <c r="U39" t="s">
+      <c r="X39" t="s">
         <v>83</v>
       </c>
-      <c r="V39" t="s">
+      <c r="Y39" t="s">
         <v>85</v>
       </c>
-      <c r="W39" t="s">
+      <c r="Z39" t="s">
         <v>94</v>
       </c>
-      <c r="X39" t="s">
+      <c r="AA39" t="s">
         <v>85</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="AB39" t="s">
         <v>95</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AC39" t="s">
         <v>85</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AD39" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -3224,31 +3476,31 @@
         <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G40" t="s">
         <v>49</v>
       </c>
       <c r="H40" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I40" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J40" t="s">
         <v>49</v>
       </c>
       <c r="K40" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L40" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M40" t="s">
         <v>49</v>
@@ -3257,31 +3509,31 @@
         <v>76</v>
       </c>
       <c r="O40" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P40" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>76</v>
+      </c>
+      <c r="R40" t="s">
+        <v>49</v>
+      </c>
+      <c r="S40" t="s">
         <v>73</v>
       </c>
-      <c r="Q40" t="s">
-        <v>49</v>
-      </c>
-      <c r="R40" t="s">
-        <v>49</v>
-      </c>
-      <c r="S40" t="s">
-        <v>75</v>
-      </c>
       <c r="T40" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U40" t="s">
         <v>49</v>
       </c>
       <c r="V40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X40" t="s">
         <v>49</v>
@@ -3290,13 +3542,22 @@
         <v>76</v>
       </c>
       <c r="Z40" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA40" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD40" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3307,31 +3568,31 @@
         <v>125</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F41" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G41" t="s">
         <v>49</v>
       </c>
       <c r="H41" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I41" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J41" t="s">
         <v>49</v>
       </c>
       <c r="K41" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L41" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M41" t="s">
         <v>49</v>
@@ -3340,31 +3601,31 @@
         <v>76</v>
       </c>
       <c r="O41" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P41" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>76</v>
+      </c>
+      <c r="R41" t="s">
+        <v>49</v>
+      </c>
+      <c r="S41" t="s">
         <v>73</v>
       </c>
-      <c r="Q41" t="s">
-        <v>49</v>
-      </c>
-      <c r="R41" t="s">
-        <v>49</v>
-      </c>
-      <c r="S41" t="s">
-        <v>75</v>
-      </c>
       <c r="T41" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U41" t="s">
         <v>49</v>
       </c>
       <c r="V41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X41" t="s">
         <v>49</v>
@@ -3373,13 +3634,22 @@
         <v>76</v>
       </c>
       <c r="Z41" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD41" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -3390,31 +3660,31 @@
         <v>125</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E42" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F42" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G42" t="s">
         <v>49</v>
       </c>
       <c r="H42" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I42" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J42" t="s">
         <v>49</v>
       </c>
       <c r="K42" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L42" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M42" t="s">
         <v>49</v>
@@ -3423,31 +3693,31 @@
         <v>76</v>
       </c>
       <c r="O42" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P42" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>76</v>
+      </c>
+      <c r="R42" t="s">
+        <v>49</v>
+      </c>
+      <c r="S42" t="s">
         <v>73</v>
       </c>
-      <c r="Q42" t="s">
-        <v>49</v>
-      </c>
-      <c r="R42" t="s">
-        <v>49</v>
-      </c>
-      <c r="S42" t="s">
-        <v>75</v>
-      </c>
       <c r="T42" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U42" t="s">
         <v>49</v>
       </c>
       <c r="V42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X42" t="s">
         <v>49</v>
@@ -3456,13 +3726,22 @@
         <v>76</v>
       </c>
       <c r="Z42" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD42" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -3473,31 +3752,31 @@
         <v>125</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G43" t="s">
         <v>49</v>
       </c>
       <c r="H43" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I43" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J43" t="s">
         <v>49</v>
       </c>
       <c r="K43" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L43" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M43" t="s">
         <v>49</v>
@@ -3506,31 +3785,31 @@
         <v>76</v>
       </c>
       <c r="O43" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P43" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>76</v>
+      </c>
+      <c r="R43" t="s">
+        <v>49</v>
+      </c>
+      <c r="S43" t="s">
         <v>73</v>
       </c>
-      <c r="Q43" t="s">
-        <v>49</v>
-      </c>
-      <c r="R43" t="s">
-        <v>49</v>
-      </c>
-      <c r="S43" t="s">
-        <v>75</v>
-      </c>
       <c r="T43" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U43" t="s">
         <v>49</v>
       </c>
       <c r="V43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X43" t="s">
         <v>49</v>
@@ -3539,13 +3818,22 @@
         <v>76</v>
       </c>
       <c r="Z43" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD43" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -3556,31 +3844,31 @@
         <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E44" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F44" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G44" t="s">
         <v>49</v>
       </c>
       <c r="H44" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I44" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J44" t="s">
         <v>49</v>
       </c>
       <c r="K44" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L44" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M44" t="s">
         <v>49</v>
@@ -3589,31 +3877,31 @@
         <v>76</v>
       </c>
       <c r="O44" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P44" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>76</v>
+      </c>
+      <c r="R44" t="s">
+        <v>49</v>
+      </c>
+      <c r="S44" t="s">
         <v>73</v>
       </c>
-      <c r="Q44" t="s">
-        <v>49</v>
-      </c>
-      <c r="R44" t="s">
-        <v>49</v>
-      </c>
-      <c r="S44" t="s">
-        <v>75</v>
-      </c>
       <c r="T44" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U44" t="s">
         <v>49</v>
       </c>
       <c r="V44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X44" t="s">
         <v>49</v>
@@ -3622,13 +3910,22 @@
         <v>76</v>
       </c>
       <c r="Z44" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD44" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>68</v>
       </c>
@@ -3639,31 +3936,31 @@
         <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F45" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G45" t="s">
         <v>49</v>
       </c>
       <c r="H45" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J45" t="s">
         <v>49</v>
       </c>
       <c r="K45" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L45" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M45" t="s">
         <v>49</v>
@@ -3672,31 +3969,31 @@
         <v>76</v>
       </c>
       <c r="O45" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P45" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>76</v>
+      </c>
+      <c r="R45" t="s">
+        <v>49</v>
+      </c>
+      <c r="S45" t="s">
         <v>73</v>
       </c>
-      <c r="Q45" t="s">
-        <v>49</v>
-      </c>
-      <c r="R45" t="s">
-        <v>49</v>
-      </c>
-      <c r="S45" t="s">
-        <v>75</v>
-      </c>
       <c r="T45" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U45" t="s">
         <v>49</v>
       </c>
       <c r="V45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X45" t="s">
         <v>49</v>
@@ -3705,13 +4002,22 @@
         <v>76</v>
       </c>
       <c r="Z45" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD45" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -3722,31 +4028,31 @@
         <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G46" t="s">
         <v>49</v>
       </c>
       <c r="H46" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I46" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J46" t="s">
         <v>49</v>
       </c>
       <c r="K46" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L46" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M46" t="s">
         <v>49</v>
@@ -3755,31 +4061,31 @@
         <v>76</v>
       </c>
       <c r="O46" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P46" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>76</v>
+      </c>
+      <c r="R46" t="s">
+        <v>49</v>
+      </c>
+      <c r="S46" t="s">
         <v>73</v>
       </c>
-      <c r="Q46" t="s">
-        <v>49</v>
-      </c>
-      <c r="R46" t="s">
-        <v>49</v>
-      </c>
-      <c r="S46" t="s">
-        <v>75</v>
-      </c>
       <c r="T46" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U46" t="s">
         <v>49</v>
       </c>
       <c r="V46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X46" t="s">
         <v>49</v>
@@ -3788,13 +4094,22 @@
         <v>76</v>
       </c>
       <c r="Z46" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA46" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD46" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -3805,31 +4120,31 @@
         <v>126</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E47" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F47" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="G47" t="s">
         <v>49</v>
       </c>
       <c r="H47" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I47" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J47" t="s">
         <v>49</v>
       </c>
       <c r="K47" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L47" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M47" t="s">
         <v>49</v>
@@ -3838,31 +4153,31 @@
         <v>76</v>
       </c>
       <c r="O47" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P47" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>76</v>
+      </c>
+      <c r="R47" t="s">
+        <v>49</v>
+      </c>
+      <c r="S47" t="s">
         <v>73</v>
       </c>
-      <c r="Q47" t="s">
-        <v>49</v>
-      </c>
-      <c r="R47" t="s">
-        <v>49</v>
-      </c>
-      <c r="S47" t="s">
-        <v>75</v>
-      </c>
       <c r="T47" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U47" t="s">
         <v>49</v>
       </c>
       <c r="V47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X47" t="s">
         <v>49</v>
@@ -3871,13 +4186,22 @@
         <v>76</v>
       </c>
       <c r="Z47" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD47" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -3888,31 +4212,31 @@
         <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F48" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G48" t="s">
         <v>49</v>
       </c>
       <c r="H48" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I48" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J48" t="s">
         <v>49</v>
       </c>
       <c r="K48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M48" t="s">
         <v>49</v>
@@ -3921,31 +4245,31 @@
         <v>76</v>
       </c>
       <c r="O48" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P48" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>76</v>
+      </c>
+      <c r="R48" t="s">
+        <v>49</v>
+      </c>
+      <c r="S48" t="s">
         <v>73</v>
       </c>
-      <c r="Q48" t="s">
-        <v>49</v>
-      </c>
-      <c r="R48" t="s">
-        <v>49</v>
-      </c>
-      <c r="S48" t="s">
-        <v>75</v>
-      </c>
       <c r="T48" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U48" t="s">
         <v>49</v>
       </c>
       <c r="V48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X48" t="s">
         <v>49</v>
@@ -3954,13 +4278,22 @@
         <v>76</v>
       </c>
       <c r="Z48" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD48" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3971,31 +4304,31 @@
         <v>126</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F49" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="G49" t="s">
         <v>49</v>
       </c>
       <c r="H49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J49" t="s">
         <v>49</v>
       </c>
       <c r="K49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M49" t="s">
         <v>49</v>
@@ -4004,31 +4337,31 @@
         <v>76</v>
       </c>
       <c r="O49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P49" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>76</v>
+      </c>
+      <c r="R49" t="s">
+        <v>49</v>
+      </c>
+      <c r="S49" t="s">
         <v>73</v>
       </c>
-      <c r="Q49" t="s">
-        <v>49</v>
-      </c>
-      <c r="R49" t="s">
-        <v>49</v>
-      </c>
-      <c r="S49" t="s">
-        <v>75</v>
-      </c>
       <c r="T49" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U49" t="s">
         <v>49</v>
       </c>
       <c r="V49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X49" t="s">
         <v>49</v>
@@ -4037,13 +4370,22 @@
         <v>76</v>
       </c>
       <c r="Z49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD49" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -4054,31 +4396,31 @@
         <v>126</v>
       </c>
       <c r="D50" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E50" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="G50" t="s">
         <v>49</v>
       </c>
       <c r="H50" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J50" t="s">
         <v>49</v>
       </c>
       <c r="K50" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L50" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M50" t="s">
         <v>49</v>
@@ -4087,31 +4429,31 @@
         <v>76</v>
       </c>
       <c r="O50" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P50" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>76</v>
+      </c>
+      <c r="R50" t="s">
+        <v>49</v>
+      </c>
+      <c r="S50" t="s">
         <v>73</v>
       </c>
-      <c r="Q50" t="s">
-        <v>49</v>
-      </c>
-      <c r="R50" t="s">
-        <v>49</v>
-      </c>
-      <c r="S50" t="s">
-        <v>75</v>
-      </c>
       <c r="T50" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U50" t="s">
         <v>49</v>
       </c>
       <c r="V50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X50" t="s">
         <v>49</v>
@@ -4120,13 +4462,22 @@
         <v>76</v>
       </c>
       <c r="Z50" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD50" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -4137,31 +4488,31 @@
         <v>125</v>
       </c>
       <c r="D51" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F51" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G51" t="s">
         <v>49</v>
       </c>
       <c r="H51" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I51" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J51" t="s">
         <v>49</v>
       </c>
       <c r="K51" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L51" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M51" t="s">
         <v>49</v>
@@ -4170,31 +4521,31 @@
         <v>76</v>
       </c>
       <c r="O51" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P51" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>76</v>
+      </c>
+      <c r="R51" t="s">
+        <v>49</v>
+      </c>
+      <c r="S51" t="s">
         <v>73</v>
       </c>
-      <c r="Q51" t="s">
-        <v>49</v>
-      </c>
-      <c r="R51" t="s">
-        <v>49</v>
-      </c>
-      <c r="S51" t="s">
-        <v>75</v>
-      </c>
       <c r="T51" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U51" t="s">
         <v>49</v>
       </c>
       <c r="V51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X51" t="s">
         <v>49</v>
@@ -4203,13 +4554,22 @@
         <v>76</v>
       </c>
       <c r="Z51" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD51" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -4220,31 +4580,31 @@
         <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E52" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F52" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="G52" t="s">
         <v>49</v>
       </c>
       <c r="H52" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I52" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J52" t="s">
         <v>49</v>
       </c>
       <c r="K52" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L52" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M52" t="s">
         <v>49</v>
@@ -4253,31 +4613,31 @@
         <v>76</v>
       </c>
       <c r="O52" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P52" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>76</v>
+      </c>
+      <c r="R52" t="s">
+        <v>49</v>
+      </c>
+      <c r="S52" t="s">
         <v>73</v>
       </c>
-      <c r="Q52" t="s">
-        <v>49</v>
-      </c>
-      <c r="R52" t="s">
-        <v>49</v>
-      </c>
-      <c r="S52" t="s">
-        <v>75</v>
-      </c>
       <c r="T52" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U52" t="s">
         <v>49</v>
       </c>
       <c r="V52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X52" t="s">
         <v>49</v>
@@ -4286,13 +4646,22 @@
         <v>76</v>
       </c>
       <c r="Z52" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD52" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -4303,31 +4672,31 @@
         <v>126</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="F53" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="G53" t="s">
         <v>49</v>
       </c>
       <c r="H53" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I53" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J53" t="s">
         <v>49</v>
       </c>
       <c r="K53" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L53" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M53" t="s">
         <v>49</v>
@@ -4336,31 +4705,31 @@
         <v>76</v>
       </c>
       <c r="O53" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P53" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>76</v>
+      </c>
+      <c r="R53" t="s">
+        <v>49</v>
+      </c>
+      <c r="S53" t="s">
         <v>73</v>
       </c>
-      <c r="Q53" t="s">
-        <v>49</v>
-      </c>
-      <c r="R53" t="s">
-        <v>49</v>
-      </c>
-      <c r="S53" t="s">
-        <v>75</v>
-      </c>
       <c r="T53" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U53" t="s">
         <v>49</v>
       </c>
       <c r="V53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X53" t="s">
         <v>49</v>
@@ -4369,13 +4738,22 @@
         <v>76</v>
       </c>
       <c r="Z53" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD53" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -4386,31 +4764,31 @@
         <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F54" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G54" t="s">
         <v>49</v>
       </c>
       <c r="H54" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I54" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J54" t="s">
         <v>49</v>
       </c>
       <c r="K54" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L54" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M54" t="s">
         <v>49</v>
@@ -4419,31 +4797,31 @@
         <v>76</v>
       </c>
       <c r="O54" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P54" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>76</v>
+      </c>
+      <c r="R54" t="s">
+        <v>49</v>
+      </c>
+      <c r="S54" t="s">
         <v>73</v>
       </c>
-      <c r="Q54" t="s">
-        <v>49</v>
-      </c>
-      <c r="R54" t="s">
-        <v>49</v>
-      </c>
-      <c r="S54" t="s">
-        <v>75</v>
-      </c>
       <c r="T54" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U54" t="s">
         <v>49</v>
       </c>
       <c r="V54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X54" t="s">
         <v>49</v>
@@ -4452,13 +4830,22 @@
         <v>76</v>
       </c>
       <c r="Z54" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD54" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -4469,31 +4856,31 @@
         <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F55" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G55" t="s">
         <v>49</v>
       </c>
       <c r="H55" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I55" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J55" t="s">
         <v>49</v>
       </c>
       <c r="K55" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L55" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M55" t="s">
         <v>49</v>
@@ -4502,31 +4889,31 @@
         <v>76</v>
       </c>
       <c r="O55" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P55" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>76</v>
+      </c>
+      <c r="R55" t="s">
+        <v>49</v>
+      </c>
+      <c r="S55" t="s">
         <v>73</v>
       </c>
-      <c r="Q55" t="s">
-        <v>49</v>
-      </c>
-      <c r="R55" t="s">
-        <v>49</v>
-      </c>
-      <c r="S55" t="s">
-        <v>75</v>
-      </c>
       <c r="T55" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U55" t="s">
         <v>49</v>
       </c>
       <c r="V55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X55" t="s">
         <v>49</v>
@@ -4535,13 +4922,22 @@
         <v>76</v>
       </c>
       <c r="Z55" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD55" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -4552,31 +4948,31 @@
         <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="E56" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G56" t="s">
         <v>49</v>
       </c>
       <c r="H56" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I56" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J56" t="s">
         <v>49</v>
       </c>
       <c r="K56" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="L56" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="M56" t="s">
         <v>49</v>
@@ -4585,31 +4981,31 @@
         <v>76</v>
       </c>
       <c r="O56" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="P56" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>76</v>
+      </c>
+      <c r="R56" t="s">
+        <v>49</v>
+      </c>
+      <c r="S56" t="s">
         <v>73</v>
       </c>
-      <c r="Q56" t="s">
-        <v>49</v>
-      </c>
-      <c r="R56" t="s">
-        <v>49</v>
-      </c>
-      <c r="S56" t="s">
-        <v>75</v>
-      </c>
       <c r="T56" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="U56" t="s">
         <v>49</v>
       </c>
       <c r="V56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X56" t="s">
         <v>49</v>
@@ -4618,13 +5014,22 @@
         <v>76</v>
       </c>
       <c r="Z56" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AA56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD56" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>117</v>
       </c>
@@ -4634,8 +5039,17 @@
       <c r="C57" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D57" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" t="s">
+        <v>130</v>
+      </c>
+      <c r="F57" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>119</v>
       </c>
@@ -4645,8 +5059,17 @@
       <c r="C58" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>120</v>
       </c>
@@ -4656,8 +5079,17 @@
       <c r="C59" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D59" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>121</v>
       </c>
@@ -4667,10 +5099,19 @@
       <c r="C60" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="D60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J39" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J39">
+  <autoFilter ref="A1:M39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M39">
       <sortCondition ref="B1:B39"/>
     </sortState>
   </autoFilter>

--- a/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
+++ b/mes_north_sea/clean_data/new_technologies/NewTechnologies_2040.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maiant/PycharmProjects/Key-Infrastructure-North-Sea-CodeAndData/mes_north_sea/clean_data/new_technologies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F23B9AD-F098-4541-B914-5DDB019DD30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B27F1C1-BD4F-5C42-93C8-635DF656712C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{64A87C74-33CB-4EAC-BDF2-6E9087B161C6}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NewTechnologies!$A$1:$N$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="133">
   <si>
     <t>Electrolyser_PEM_offshore</t>
   </si>
@@ -436,6 +436,9 @@
   </si>
   <si>
     <t>Offshore_Wind, PermanentStorage_CO2_simple</t>
+  </si>
+  <si>
+    <t>RE_only_no_space</t>
   </si>
 </sst>
 </file>
@@ -779,24 +782,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD60"/>
+  <dimension ref="A1:AE60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="15.33203125" customWidth="1"/>
-    <col min="14" max="14" width="43" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="43" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="15.33203125" customWidth="1"/>
-    <col min="23" max="23" width="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="43" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="43" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" customWidth="1"/>
+    <col min="24" max="24" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -816,398 +819,401 @@
         <v>129</v>
       </c>
       <c r="G1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" t="s">
         <v>86</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>87</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>113</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>114</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>115</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>47</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>88</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>89</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>90</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>91</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>48</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <f>C1&amp;"_no_onshore_wind"</f>
         <v>RE_only_no_onshore_wind</v>
       </c>
-      <c r="U1" t="str">
-        <f>G1&amp;"_no_onshore_wind"</f>
-        <v>Battery_on_no_onshore_wind</v>
-      </c>
       <c r="V1" t="str">
         <f>H1&amp;"_no_onshore_wind"</f>
-        <v>Battery_off_no_onshore_wind</v>
+        <v>Battery_on_no_onshore_wind</v>
       </c>
       <c r="W1" t="str">
         <f>I1&amp;"_no_onshore_wind"</f>
-        <v>Battery_all_no_onshore_wind</v>
+        <v>Battery_off_no_onshore_wind</v>
       </c>
       <c r="X1" t="str">
         <f>J1&amp;"_no_onshore_wind"</f>
+        <v>Battery_all_no_onshore_wind</v>
+      </c>
+      <c r="Y1" t="str">
+        <f>K1&amp;"_no_onshore_wind"</f>
         <v>ElectricityGrid_all_no_onshore_wind</v>
       </c>
-      <c r="Y1" t="str">
-        <f t="shared" ref="Y1:AD1" si="0">N1&amp;"_no_onshore_wind"</f>
+      <c r="Z1" t="str">
+        <f t="shared" ref="Z1:AE1" si="0">O1&amp;"_no_onshore_wind"</f>
         <v>Hydrogen_Baseline_no_onshore_wind</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AA1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H1_no_onshore_wind</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AB1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H2_no_onshore_wind</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AC1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H3_no_onshore_wind</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AD1" t="str">
         <f t="shared" si="0"/>
         <v>Hydrogen_H4_no_onshore_wind</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AE1" t="str">
         <f t="shared" si="0"/>
         <v>All_no_onshore_wind</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
       <c r="I2" t="s">
         <v>45</v>
       </c>
-      <c r="N2" t="s">
-        <v>0</v>
+      <c r="J2" t="s">
+        <v>45</v>
       </c>
       <c r="O2" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
         <v>69</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
       <c r="W2" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" t="s">
-        <v>0</v>
+      <c r="X2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="s">
         <v>0</v>
       </c>
-      <c r="AB2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AA2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" t="s">
-        <v>45</v>
-      </c>
       <c r="I3" t="s">
         <v>45</v>
       </c>
-      <c r="N3" t="s">
-        <v>0</v>
+      <c r="J3" t="s">
+        <v>45</v>
       </c>
       <c r="O3" t="s">
         <v>0</v>
       </c>
-      <c r="Q3" t="s">
-        <v>0</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="P3" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
         <v>69</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
       <c r="W3" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" t="s">
-        <v>0</v>
+      <c r="X3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="s">
         <v>0</v>
       </c>
-      <c r="AB3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="AA3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
-        <v>45</v>
-      </c>
       <c r="I4" t="s">
         <v>45</v>
       </c>
-      <c r="N4" t="s">
-        <v>0</v>
+      <c r="J4" t="s">
+        <v>45</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
-        <v>0</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="P4" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
         <v>69</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
       <c r="W4" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" t="s">
-        <v>0</v>
+      <c r="X4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="s">
         <v>0</v>
       </c>
-      <c r="AB4" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="AA4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
       <c r="I5" t="s">
         <v>45</v>
       </c>
-      <c r="N5" t="s">
-        <v>0</v>
+      <c r="J5" t="s">
+        <v>45</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
       </c>
-      <c r="Q5" t="s">
-        <v>0</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="P5" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
         <v>69</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
       <c r="W5" t="s">
         <v>45</v>
       </c>
-      <c r="Y5" t="s">
-        <v>0</v>
+      <c r="X5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="s">
         <v>0</v>
       </c>
-      <c r="AB5" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="s">
+      <c r="AA5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>45</v>
-      </c>
       <c r="I6" t="s">
         <v>45</v>
       </c>
-      <c r="N6" t="s">
-        <v>0</v>
+      <c r="J6" t="s">
+        <v>45</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
       </c>
-      <c r="Q6" t="s">
-        <v>0</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="P6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6" t="s">
         <v>69</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
       <c r="W6" t="s">
         <v>45</v>
       </c>
-      <c r="Y6" t="s">
-        <v>0</v>
+      <c r="X6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="s">
         <v>0</v>
       </c>
-      <c r="AB6" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AA6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
       <c r="I7" t="s">
         <v>45</v>
       </c>
-      <c r="N7" t="s">
-        <v>0</v>
+      <c r="J7" t="s">
+        <v>45</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
       </c>
-      <c r="Q7" t="s">
-        <v>0</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="P7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
         <v>69</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
       <c r="W7" t="s">
         <v>45</v>
       </c>
-      <c r="Y7" t="s">
-        <v>0</v>
+      <c r="X7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="s">
         <v>0</v>
       </c>
-      <c r="AB7" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="s">
+      <c r="AA7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
       <c r="I8" t="s">
         <v>45</v>
       </c>
-      <c r="N8" t="s">
-        <v>0</v>
+      <c r="J8" t="s">
+        <v>45</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
       </c>
-      <c r="Q8" t="s">
-        <v>0</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T8" t="s">
         <v>69</v>
       </c>
-      <c r="V8" t="s">
-        <v>45</v>
-      </c>
       <c r="W8" t="s">
         <v>45</v>
       </c>
-      <c r="Y8" t="s">
-        <v>0</v>
+      <c r="X8" t="s">
+        <v>45</v>
       </c>
       <c r="Z8" t="s">
         <v>0</v>
       </c>
-      <c r="AB8" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="s">
+      <c r="AA8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1226,88 +1232,91 @@
       <c r="F9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H9" t="s">
-        <v>45</v>
+      <c r="G9" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I9" t="s">
         <v>45</v>
       </c>
-      <c r="N9" t="s">
-        <v>0</v>
+      <c r="J9" t="s">
+        <v>45</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
       </c>
-      <c r="Q9" t="s">
-        <v>0</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="P9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>0</v>
+      </c>
+      <c r="T9" t="s">
         <v>69</v>
       </c>
-      <c r="V9" t="s">
-        <v>45</v>
-      </c>
       <c r="W9" t="s">
         <v>45</v>
       </c>
-      <c r="Y9" t="s">
-        <v>0</v>
+      <c r="X9" t="s">
+        <v>45</v>
       </c>
       <c r="Z9" t="s">
         <v>0</v>
       </c>
-      <c r="AB9" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="s">
+      <c r="AA9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="H10" t="s">
-        <v>45</v>
-      </c>
       <c r="I10" t="s">
         <v>45</v>
       </c>
-      <c r="N10" t="s">
-        <v>0</v>
+      <c r="J10" t="s">
+        <v>45</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
       </c>
-      <c r="Q10" t="s">
-        <v>0</v>
-      </c>
-      <c r="S10" t="s">
+      <c r="P10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10" t="s">
         <v>69</v>
       </c>
-      <c r="V10" t="s">
-        <v>45</v>
-      </c>
       <c r="W10" t="s">
         <v>45</v>
       </c>
-      <c r="Y10" t="s">
-        <v>0</v>
+      <c r="X10" t="s">
+        <v>45</v>
       </c>
       <c r="Z10" t="s">
         <v>0</v>
       </c>
-      <c r="AB10" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="s">
+      <c r="AA10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1326,44 +1335,47 @@
       <c r="F11" t="s">
         <v>130</v>
       </c>
-      <c r="H11" t="s">
-        <v>45</v>
+      <c r="G11" t="s">
+        <v>122</v>
       </c>
       <c r="I11" t="s">
         <v>45</v>
       </c>
-      <c r="N11" t="s">
-        <v>0</v>
+      <c r="J11" t="s">
+        <v>45</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
       </c>
-      <c r="Q11" t="s">
-        <v>0</v>
-      </c>
-      <c r="S11" t="s">
+      <c r="P11" t="s">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
         <v>69</v>
       </c>
-      <c r="V11" t="s">
-        <v>45</v>
-      </c>
       <c r="W11" t="s">
         <v>45</v>
       </c>
-      <c r="Y11" t="s">
-        <v>0</v>
+      <c r="X11" t="s">
+        <v>45</v>
       </c>
       <c r="Z11" t="s">
         <v>0</v>
       </c>
-      <c r="AB11" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="s">
+      <c r="AA11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1382,44 +1394,47 @@
       <c r="F12" t="s">
         <v>130</v>
       </c>
-      <c r="H12" t="s">
-        <v>45</v>
+      <c r="G12" t="s">
+        <v>122</v>
       </c>
       <c r="I12" t="s">
         <v>45</v>
       </c>
-      <c r="N12" t="s">
-        <v>0</v>
+      <c r="J12" t="s">
+        <v>45</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
       </c>
-      <c r="Q12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S12" t="s">
+      <c r="P12" t="s">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
         <v>69</v>
       </c>
-      <c r="V12" t="s">
-        <v>45</v>
-      </c>
       <c r="W12" t="s">
         <v>45</v>
       </c>
-      <c r="Y12" t="s">
-        <v>0</v>
+      <c r="X12" t="s">
+        <v>45</v>
       </c>
       <c r="Z12" t="s">
         <v>0</v>
       </c>
-      <c r="AB12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="s">
+      <c r="AA12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1438,44 +1453,47 @@
       <c r="F13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H13" t="s">
-        <v>45</v>
+      <c r="G13" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="I13" t="s">
         <v>45</v>
       </c>
-      <c r="N13" t="s">
-        <v>0</v>
+      <c r="J13" t="s">
+        <v>45</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
       </c>
-      <c r="Q13" t="s">
-        <v>0</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="P13" t="s">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>0</v>
+      </c>
+      <c r="T13" t="s">
         <v>69</v>
       </c>
-      <c r="V13" t="s">
-        <v>45</v>
-      </c>
       <c r="W13" t="s">
         <v>45</v>
       </c>
-      <c r="Y13" t="s">
-        <v>0</v>
+      <c r="X13" t="s">
+        <v>45</v>
       </c>
       <c r="Z13" t="s">
         <v>0</v>
       </c>
-      <c r="AB13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="s">
+      <c r="AA13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1488,44 +1506,47 @@
       <c r="D14" t="s">
         <v>123</v>
       </c>
-      <c r="H14" t="s">
-        <v>45</v>
+      <c r="G14" t="s">
+        <v>123</v>
       </c>
       <c r="I14" t="s">
         <v>45</v>
       </c>
-      <c r="N14" t="s">
-        <v>0</v>
+      <c r="J14" t="s">
+        <v>45</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
       </c>
-      <c r="Q14" t="s">
-        <v>0</v>
-      </c>
-      <c r="S14" t="s">
+      <c r="P14" t="s">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
         <v>69</v>
       </c>
-      <c r="V14" t="s">
-        <v>45</v>
-      </c>
       <c r="W14" t="s">
         <v>45</v>
       </c>
-      <c r="Y14" t="s">
-        <v>0</v>
+      <c r="X14" t="s">
+        <v>45</v>
       </c>
       <c r="Z14" t="s">
         <v>0</v>
       </c>
-      <c r="AB14" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="s">
+      <c r="AA14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1538,44 +1559,47 @@
       <c r="D15" t="s">
         <v>123</v>
       </c>
-      <c r="H15" t="s">
-        <v>45</v>
+      <c r="G15" t="s">
+        <v>123</v>
       </c>
       <c r="I15" t="s">
         <v>45</v>
       </c>
-      <c r="N15" t="s">
-        <v>0</v>
+      <c r="J15" t="s">
+        <v>45</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
       </c>
-      <c r="Q15" t="s">
-        <v>0</v>
-      </c>
-      <c r="S15" t="s">
+      <c r="P15" t="s">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>0</v>
+      </c>
+      <c r="T15" t="s">
         <v>69</v>
       </c>
-      <c r="V15" t="s">
-        <v>45</v>
-      </c>
       <c r="W15" t="s">
         <v>45</v>
       </c>
-      <c r="Y15" t="s">
-        <v>0</v>
+      <c r="X15" t="s">
+        <v>45</v>
       </c>
       <c r="Z15" t="s">
         <v>0</v>
       </c>
-      <c r="AB15" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="s">
+      <c r="AA15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1588,44 +1612,47 @@
       <c r="D16" t="s">
         <v>123</v>
       </c>
-      <c r="H16" t="s">
-        <v>45</v>
+      <c r="G16" t="s">
+        <v>123</v>
       </c>
       <c r="I16" t="s">
         <v>45</v>
       </c>
-      <c r="N16" t="s">
-        <v>0</v>
+      <c r="J16" t="s">
+        <v>45</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
       </c>
-      <c r="Q16" t="s">
-        <v>0</v>
-      </c>
-      <c r="S16" t="s">
+      <c r="P16" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
         <v>69</v>
       </c>
-      <c r="V16" t="s">
-        <v>45</v>
-      </c>
       <c r="W16" t="s">
         <v>45</v>
       </c>
-      <c r="Y16" t="s">
-        <v>0</v>
+      <c r="X16" t="s">
+        <v>45</v>
       </c>
       <c r="Z16" t="s">
         <v>0</v>
       </c>
-      <c r="AB16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="s">
+      <c r="AA16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1638,44 +1665,47 @@
       <c r="D17" t="s">
         <v>123</v>
       </c>
-      <c r="H17" t="s">
-        <v>45</v>
+      <c r="G17" t="s">
+        <v>123</v>
       </c>
       <c r="I17" t="s">
         <v>45</v>
       </c>
-      <c r="N17" t="s">
-        <v>0</v>
+      <c r="J17" t="s">
+        <v>45</v>
       </c>
       <c r="O17" t="s">
         <v>0</v>
       </c>
-      <c r="Q17" t="s">
-        <v>0</v>
-      </c>
-      <c r="S17" t="s">
+      <c r="P17" t="s">
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17" t="s">
         <v>69</v>
       </c>
-      <c r="V17" t="s">
-        <v>45</v>
-      </c>
       <c r="W17" t="s">
         <v>45</v>
       </c>
-      <c r="Y17" t="s">
-        <v>0</v>
+      <c r="X17" t="s">
+        <v>45</v>
       </c>
       <c r="Z17" t="s">
         <v>0</v>
       </c>
-      <c r="AB17" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="s">
+      <c r="AA17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1688,44 +1718,47 @@
       <c r="D18" t="s">
         <v>123</v>
       </c>
-      <c r="H18" t="s">
-        <v>45</v>
+      <c r="G18" t="s">
+        <v>123</v>
       </c>
       <c r="I18" t="s">
         <v>45</v>
       </c>
-      <c r="N18" t="s">
-        <v>0</v>
+      <c r="J18" t="s">
+        <v>45</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
       </c>
-      <c r="Q18" t="s">
-        <v>0</v>
-      </c>
-      <c r="S18" t="s">
+      <c r="P18" t="s">
+        <v>0</v>
+      </c>
+      <c r="R18" t="s">
+        <v>0</v>
+      </c>
+      <c r="T18" t="s">
         <v>69</v>
       </c>
-      <c r="V18" t="s">
-        <v>45</v>
-      </c>
       <c r="W18" t="s">
         <v>45</v>
       </c>
-      <c r="Y18" t="s">
-        <v>0</v>
+      <c r="X18" t="s">
+        <v>45</v>
       </c>
       <c r="Z18" t="s">
         <v>0</v>
       </c>
-      <c r="AB18" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="s">
+      <c r="AA18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1738,44 +1771,47 @@
       <c r="D19" t="s">
         <v>123</v>
       </c>
-      <c r="H19" t="s">
-        <v>45</v>
+      <c r="G19" t="s">
+        <v>123</v>
       </c>
       <c r="I19" t="s">
         <v>45</v>
       </c>
-      <c r="N19" t="s">
-        <v>0</v>
+      <c r="J19" t="s">
+        <v>45</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
       </c>
-      <c r="Q19" t="s">
-        <v>0</v>
-      </c>
-      <c r="S19" t="s">
+      <c r="P19" t="s">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>0</v>
+      </c>
+      <c r="T19" t="s">
         <v>69</v>
       </c>
-      <c r="V19" t="s">
-        <v>45</v>
-      </c>
       <c r="W19" t="s">
         <v>45</v>
       </c>
-      <c r="Y19" t="s">
-        <v>0</v>
+      <c r="X19" t="s">
+        <v>45</v>
       </c>
       <c r="Z19" t="s">
         <v>0</v>
       </c>
-      <c r="AB19" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="s">
+      <c r="AA19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1794,44 +1830,47 @@
       <c r="F20" t="s">
         <v>130</v>
       </c>
-      <c r="H20" t="s">
-        <v>45</v>
+      <c r="G20" t="s">
+        <v>124</v>
       </c>
       <c r="I20" t="s">
         <v>45</v>
       </c>
-      <c r="N20" t="s">
-        <v>0</v>
+      <c r="J20" t="s">
+        <v>45</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
-      <c r="Q20" t="s">
-        <v>0</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="P20" t="s">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
+        <v>0</v>
+      </c>
+      <c r="T20" t="s">
         <v>69</v>
       </c>
-      <c r="V20" t="s">
-        <v>45</v>
-      </c>
       <c r="W20" t="s">
         <v>45</v>
       </c>
-      <c r="Y20" t="s">
-        <v>0</v>
+      <c r="X20" t="s">
+        <v>45</v>
       </c>
       <c r="Z20" t="s">
         <v>0</v>
       </c>
-      <c r="AB20" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="s">
+      <c r="AA20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1850,44 +1889,47 @@
       <c r="F21" t="s">
         <v>130</v>
       </c>
-      <c r="H21" t="s">
-        <v>45</v>
+      <c r="G21" t="s">
+        <v>124</v>
       </c>
       <c r="I21" t="s">
         <v>45</v>
       </c>
-      <c r="N21" t="s">
-        <v>0</v>
+      <c r="J21" t="s">
+        <v>45</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
-      <c r="Q21" t="s">
-        <v>0</v>
-      </c>
-      <c r="S21" t="s">
+      <c r="P21" t="s">
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
+        <v>0</v>
+      </c>
+      <c r="T21" t="s">
         <v>69</v>
       </c>
-      <c r="V21" t="s">
-        <v>45</v>
-      </c>
       <c r="W21" t="s">
         <v>45</v>
       </c>
-      <c r="Y21" t="s">
-        <v>0</v>
+      <c r="X21" t="s">
+        <v>45</v>
       </c>
       <c r="Z21" t="s">
         <v>0</v>
       </c>
-      <c r="AB21" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="s">
+      <c r="AA21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1900,44 +1942,47 @@
       <c r="D22" t="s">
         <v>123</v>
       </c>
-      <c r="H22" t="s">
-        <v>45</v>
+      <c r="G22" t="s">
+        <v>123</v>
       </c>
       <c r="I22" t="s">
         <v>45</v>
       </c>
-      <c r="N22" t="s">
-        <v>0</v>
+      <c r="J22" t="s">
+        <v>45</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
-      <c r="Q22" t="s">
-        <v>0</v>
-      </c>
-      <c r="S22" t="s">
+      <c r="P22" t="s">
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
+        <v>0</v>
+      </c>
+      <c r="T22" t="s">
         <v>69</v>
       </c>
-      <c r="V22" t="s">
-        <v>45</v>
-      </c>
       <c r="W22" t="s">
         <v>45</v>
       </c>
-      <c r="Y22" t="s">
-        <v>0</v>
+      <c r="X22" t="s">
+        <v>45</v>
       </c>
       <c r="Z22" t="s">
         <v>0</v>
       </c>
-      <c r="AB22" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="s">
+      <c r="AA22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1956,44 +2001,47 @@
       <c r="F23" t="s">
         <v>130</v>
       </c>
-      <c r="H23" t="s">
-        <v>45</v>
+      <c r="G23" t="s">
+        <v>124</v>
       </c>
       <c r="I23" t="s">
         <v>45</v>
       </c>
-      <c r="N23" t="s">
-        <v>0</v>
+      <c r="J23" t="s">
+        <v>45</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
       </c>
-      <c r="Q23" t="s">
-        <v>0</v>
-      </c>
-      <c r="S23" t="s">
+      <c r="P23" t="s">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>0</v>
+      </c>
+      <c r="T23" t="s">
         <v>69</v>
       </c>
-      <c r="V23" t="s">
-        <v>45</v>
-      </c>
       <c r="W23" t="s">
         <v>45</v>
       </c>
-      <c r="Y23" t="s">
-        <v>0</v>
+      <c r="X23" t="s">
+        <v>45</v>
       </c>
       <c r="Z23" t="s">
         <v>0</v>
       </c>
-      <c r="AB23" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="s">
+      <c r="AA23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -2013,17 +2061,17 @@
         <v>116</v>
       </c>
       <c r="G24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" t="s">
         <v>70</v>
       </c>
-      <c r="H24" t="s">
-        <v>65</v>
-      </c>
       <c r="I24" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" t="s">
         <v>70</v>
       </c>
-      <c r="J24" t="s">
-        <v>65</v>
-      </c>
       <c r="K24" t="s">
         <v>65</v>
       </c>
@@ -2034,58 +2082,61 @@
         <v>65</v>
       </c>
       <c r="N24" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" t="s">
         <v>71</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>92</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>71</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>93</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>71</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>72</v>
       </c>
-      <c r="T24" t="s">
+      <c r="U24" t="s">
         <v>83</v>
       </c>
-      <c r="U24" t="s">
+      <c r="V24" t="s">
         <v>84</v>
       </c>
-      <c r="V24" t="s">
+      <c r="W24" t="s">
         <v>83</v>
       </c>
-      <c r="W24" t="s">
+      <c r="X24" t="s">
         <v>84</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>83</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Z24" t="s">
         <v>85</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AA24" t="s">
         <v>94</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB24" t="s">
         <v>85</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AC24" t="s">
         <v>95</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>85</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AE24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -2105,17 +2156,17 @@
         <v>116</v>
       </c>
       <c r="G25" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" t="s">
         <v>70</v>
       </c>
-      <c r="H25" t="s">
-        <v>65</v>
-      </c>
       <c r="I25" t="s">
+        <v>65</v>
+      </c>
+      <c r="J25" t="s">
         <v>70</v>
       </c>
-      <c r="J25" t="s">
-        <v>65</v>
-      </c>
       <c r="K25" t="s">
         <v>65</v>
       </c>
@@ -2126,58 +2177,61 @@
         <v>65</v>
       </c>
       <c r="N25" t="s">
+        <v>65</v>
+      </c>
+      <c r="O25" t="s">
         <v>71</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>92</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>71</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>93</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>71</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>72</v>
       </c>
-      <c r="T25" t="s">
+      <c r="U25" t="s">
         <v>83</v>
       </c>
-      <c r="U25" t="s">
+      <c r="V25" t="s">
         <v>84</v>
       </c>
-      <c r="V25" t="s">
+      <c r="W25" t="s">
         <v>83</v>
       </c>
-      <c r="W25" t="s">
+      <c r="X25" t="s">
         <v>84</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Y25" t="s">
         <v>83</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="Z25" t="s">
         <v>85</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AA25" t="s">
         <v>94</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>85</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AC25" t="s">
         <v>95</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AD25" t="s">
         <v>85</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AE25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -2197,17 +2251,17 @@
         <v>116</v>
       </c>
       <c r="G26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" t="s">
         <v>70</v>
       </c>
-      <c r="H26" t="s">
-        <v>65</v>
-      </c>
       <c r="I26" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" t="s">
         <v>70</v>
       </c>
-      <c r="J26" t="s">
-        <v>65</v>
-      </c>
       <c r="K26" t="s">
         <v>65</v>
       </c>
@@ -2218,58 +2272,61 @@
         <v>65</v>
       </c>
       <c r="N26" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" t="s">
         <v>71</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>92</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>71</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>93</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>71</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>72</v>
       </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
         <v>83</v>
       </c>
-      <c r="U26" t="s">
+      <c r="V26" t="s">
         <v>84</v>
       </c>
-      <c r="V26" t="s">
+      <c r="W26" t="s">
         <v>83</v>
       </c>
-      <c r="W26" t="s">
+      <c r="X26" t="s">
         <v>84</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>83</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Z26" t="s">
         <v>85</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>94</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>85</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AC26" t="s">
         <v>95</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AD26" t="s">
         <v>85</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AE26" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2289,17 +2346,17 @@
         <v>116</v>
       </c>
       <c r="G27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" t="s">
         <v>70</v>
       </c>
-      <c r="H27" t="s">
-        <v>65</v>
-      </c>
       <c r="I27" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" t="s">
         <v>70</v>
       </c>
-      <c r="J27" t="s">
-        <v>65</v>
-      </c>
       <c r="K27" t="s">
         <v>65</v>
       </c>
@@ -2310,58 +2367,61 @@
         <v>65</v>
       </c>
       <c r="N27" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" t="s">
         <v>71</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>92</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>71</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>93</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>71</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
         <v>72</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>83</v>
       </c>
-      <c r="U27" t="s">
+      <c r="V27" t="s">
         <v>84</v>
       </c>
-      <c r="V27" t="s">
+      <c r="W27" t="s">
         <v>83</v>
       </c>
-      <c r="W27" t="s">
+      <c r="X27" t="s">
         <v>84</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
         <v>83</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Z27" t="s">
         <v>85</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AA27" t="s">
         <v>94</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>85</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AC27" t="s">
         <v>95</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AD27" t="s">
         <v>85</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AE27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -2381,17 +2441,17 @@
         <v>116</v>
       </c>
       <c r="G28" t="s">
+        <v>116</v>
+      </c>
+      <c r="H28" t="s">
         <v>70</v>
       </c>
-      <c r="H28" t="s">
-        <v>65</v>
-      </c>
       <c r="I28" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" t="s">
         <v>70</v>
       </c>
-      <c r="J28" t="s">
-        <v>65</v>
-      </c>
       <c r="K28" t="s">
         <v>65</v>
       </c>
@@ -2402,58 +2462,61 @@
         <v>65</v>
       </c>
       <c r="N28" t="s">
+        <v>65</v>
+      </c>
+      <c r="O28" t="s">
         <v>71</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>92</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>71</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>93</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>71</v>
       </c>
-      <c r="S28" t="s">
+      <c r="T28" t="s">
         <v>72</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U28" t="s">
         <v>83</v>
       </c>
-      <c r="U28" t="s">
+      <c r="V28" t="s">
         <v>84</v>
       </c>
-      <c r="V28" t="s">
+      <c r="W28" t="s">
         <v>83</v>
       </c>
-      <c r="W28" t="s">
+      <c r="X28" t="s">
         <v>84</v>
       </c>
-      <c r="X28" t="s">
+      <c r="Y28" t="s">
         <v>83</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Z28" t="s">
         <v>85</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AA28" t="s">
         <v>94</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>85</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>95</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AD28" t="s">
         <v>85</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AE28" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -2473,17 +2536,17 @@
         <v>116</v>
       </c>
       <c r="G29" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" t="s">
         <v>70</v>
       </c>
-      <c r="H29" t="s">
-        <v>65</v>
-      </c>
       <c r="I29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J29" t="s">
         <v>70</v>
       </c>
-      <c r="J29" t="s">
-        <v>65</v>
-      </c>
       <c r="K29" t="s">
         <v>65</v>
       </c>
@@ -2494,58 +2557,61 @@
         <v>65</v>
       </c>
       <c r="N29" t="s">
+        <v>65</v>
+      </c>
+      <c r="O29" t="s">
         <v>71</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>92</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>71</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>93</v>
       </c>
-      <c r="R29" t="s">
+      <c r="S29" t="s">
         <v>71</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>72</v>
       </c>
-      <c r="T29" t="s">
+      <c r="U29" t="s">
         <v>83</v>
       </c>
-      <c r="U29" t="s">
+      <c r="V29" t="s">
         <v>84</v>
       </c>
-      <c r="V29" t="s">
+      <c r="W29" t="s">
         <v>83</v>
       </c>
-      <c r="W29" t="s">
+      <c r="X29" t="s">
         <v>84</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Y29" t="s">
         <v>83</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Z29" t="s">
         <v>85</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AA29" t="s">
         <v>94</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>85</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
         <v>95</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AD29" t="s">
         <v>85</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AE29" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -2565,17 +2631,17 @@
         <v>116</v>
       </c>
       <c r="G30" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" t="s">
         <v>70</v>
       </c>
-      <c r="H30" t="s">
-        <v>65</v>
-      </c>
       <c r="I30" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30" t="s">
         <v>70</v>
       </c>
-      <c r="J30" t="s">
-        <v>65</v>
-      </c>
       <c r="K30" t="s">
         <v>65</v>
       </c>
@@ -2586,58 +2652,61 @@
         <v>65</v>
       </c>
       <c r="N30" t="s">
+        <v>65</v>
+      </c>
+      <c r="O30" t="s">
         <v>71</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>92</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>71</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>93</v>
       </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
         <v>71</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>72</v>
       </c>
-      <c r="T30" t="s">
+      <c r="U30" t="s">
         <v>83</v>
       </c>
-      <c r="U30" t="s">
+      <c r="V30" t="s">
         <v>84</v>
       </c>
-      <c r="V30" t="s">
+      <c r="W30" t="s">
         <v>83</v>
       </c>
-      <c r="W30" t="s">
+      <c r="X30" t="s">
         <v>84</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Y30" t="s">
         <v>83</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" t="s">
         <v>85</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>94</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>85</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
         <v>95</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AD30" t="s">
         <v>85</v>
       </c>
-      <c r="AD30" t="s">
+      <c r="AE30" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2657,17 +2726,17 @@
         <v>116</v>
       </c>
       <c r="G31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" t="s">
         <v>70</v>
       </c>
-      <c r="H31" t="s">
-        <v>65</v>
-      </c>
       <c r="I31" t="s">
+        <v>65</v>
+      </c>
+      <c r="J31" t="s">
         <v>70</v>
       </c>
-      <c r="J31" t="s">
-        <v>65</v>
-      </c>
       <c r="K31" t="s">
         <v>65</v>
       </c>
@@ -2678,58 +2747,61 @@
         <v>65</v>
       </c>
       <c r="N31" t="s">
+        <v>65</v>
+      </c>
+      <c r="O31" t="s">
         <v>71</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>92</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>71</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>93</v>
       </c>
-      <c r="R31" t="s">
+      <c r="S31" t="s">
         <v>71</v>
       </c>
-      <c r="S31" t="s">
+      <c r="T31" t="s">
         <v>72</v>
       </c>
-      <c r="T31" t="s">
+      <c r="U31" t="s">
         <v>83</v>
       </c>
-      <c r="U31" t="s">
+      <c r="V31" t="s">
         <v>84</v>
       </c>
-      <c r="V31" t="s">
+      <c r="W31" t="s">
         <v>83</v>
       </c>
-      <c r="W31" t="s">
+      <c r="X31" t="s">
         <v>84</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Y31" t="s">
         <v>83</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Z31" t="s">
         <v>85</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AA31" t="s">
         <v>94</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AB31" t="s">
         <v>85</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AC31" t="s">
         <v>95</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AD31" t="s">
         <v>85</v>
       </c>
-      <c r="AD31" t="s">
+      <c r="AE31" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2749,17 +2821,17 @@
         <v>116</v>
       </c>
       <c r="G32" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" t="s">
         <v>70</v>
       </c>
-      <c r="H32" t="s">
-        <v>65</v>
-      </c>
       <c r="I32" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" t="s">
         <v>70</v>
       </c>
-      <c r="J32" t="s">
-        <v>65</v>
-      </c>
       <c r="K32" t="s">
         <v>65</v>
       </c>
@@ -2770,58 +2842,61 @@
         <v>65</v>
       </c>
       <c r="N32" t="s">
+        <v>65</v>
+      </c>
+      <c r="O32" t="s">
         <v>71</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>92</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>71</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>93</v>
       </c>
-      <c r="R32" t="s">
+      <c r="S32" t="s">
         <v>71</v>
       </c>
-      <c r="S32" t="s">
+      <c r="T32" t="s">
         <v>72</v>
       </c>
-      <c r="T32" t="s">
+      <c r="U32" t="s">
         <v>83</v>
       </c>
-      <c r="U32" t="s">
+      <c r="V32" t="s">
         <v>84</v>
       </c>
-      <c r="V32" t="s">
+      <c r="W32" t="s">
         <v>83</v>
       </c>
-      <c r="W32" t="s">
+      <c r="X32" t="s">
         <v>84</v>
       </c>
-      <c r="X32" t="s">
+      <c r="Y32" t="s">
         <v>83</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="Z32" t="s">
         <v>85</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>94</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>85</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>95</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AD32" t="s">
         <v>85</v>
       </c>
-      <c r="AD32" t="s">
+      <c r="AE32" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2841,17 +2916,17 @@
         <v>116</v>
       </c>
       <c r="G33" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" t="s">
         <v>70</v>
       </c>
-      <c r="H33" t="s">
-        <v>65</v>
-      </c>
       <c r="I33" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33" t="s">
         <v>70</v>
       </c>
-      <c r="J33" t="s">
-        <v>65</v>
-      </c>
       <c r="K33" t="s">
         <v>65</v>
       </c>
@@ -2862,58 +2937,61 @@
         <v>65</v>
       </c>
       <c r="N33" t="s">
+        <v>65</v>
+      </c>
+      <c r="O33" t="s">
         <v>71</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>92</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>71</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>93</v>
       </c>
-      <c r="R33" t="s">
+      <c r="S33" t="s">
         <v>71</v>
       </c>
-      <c r="S33" t="s">
+      <c r="T33" t="s">
         <v>72</v>
       </c>
-      <c r="T33" t="s">
+      <c r="U33" t="s">
         <v>83</v>
       </c>
-      <c r="U33" t="s">
+      <c r="V33" t="s">
         <v>84</v>
       </c>
-      <c r="V33" t="s">
+      <c r="W33" t="s">
         <v>83</v>
       </c>
-      <c r="W33" t="s">
+      <c r="X33" t="s">
         <v>84</v>
       </c>
-      <c r="X33" t="s">
+      <c r="Y33" t="s">
         <v>83</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="Z33" t="s">
         <v>85</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
         <v>94</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AB33" t="s">
         <v>85</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AC33" t="s">
         <v>95</v>
       </c>
-      <c r="AC33" t="s">
+      <c r="AD33" t="s">
         <v>85</v>
       </c>
-      <c r="AD33" t="s">
+      <c r="AE33" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2933,17 +3011,17 @@
         <v>116</v>
       </c>
       <c r="G34" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" t="s">
         <v>70</v>
       </c>
-      <c r="H34" t="s">
-        <v>65</v>
-      </c>
       <c r="I34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34" t="s">
         <v>70</v>
       </c>
-      <c r="J34" t="s">
-        <v>65</v>
-      </c>
       <c r="K34" t="s">
         <v>65</v>
       </c>
@@ -2954,58 +3032,61 @@
         <v>65</v>
       </c>
       <c r="N34" t="s">
+        <v>65</v>
+      </c>
+      <c r="O34" t="s">
         <v>71</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>92</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>71</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>93</v>
       </c>
-      <c r="R34" t="s">
+      <c r="S34" t="s">
         <v>71</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
         <v>72</v>
       </c>
-      <c r="T34" t="s">
+      <c r="U34" t="s">
         <v>83</v>
       </c>
-      <c r="U34" t="s">
+      <c r="V34" t="s">
         <v>84</v>
       </c>
-      <c r="V34" t="s">
+      <c r="W34" t="s">
         <v>83</v>
       </c>
-      <c r="W34" t="s">
+      <c r="X34" t="s">
         <v>84</v>
       </c>
-      <c r="X34" t="s">
+      <c r="Y34" t="s">
         <v>83</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="Z34" t="s">
         <v>85</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AA34" t="s">
         <v>94</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AB34" t="s">
         <v>85</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AC34" t="s">
         <v>95</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AD34" t="s">
         <v>85</v>
       </c>
-      <c r="AD34" t="s">
+      <c r="AE34" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3025,17 +3106,17 @@
         <v>116</v>
       </c>
       <c r="G35" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" t="s">
         <v>70</v>
       </c>
-      <c r="H35" t="s">
-        <v>65</v>
-      </c>
       <c r="I35" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" t="s">
         <v>70</v>
       </c>
-      <c r="J35" t="s">
-        <v>65</v>
-      </c>
       <c r="K35" t="s">
         <v>65</v>
       </c>
@@ -3046,58 +3127,61 @@
         <v>65</v>
       </c>
       <c r="N35" t="s">
+        <v>65</v>
+      </c>
+      <c r="O35" t="s">
         <v>71</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>92</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>71</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>93</v>
       </c>
-      <c r="R35" t="s">
+      <c r="S35" t="s">
         <v>71</v>
       </c>
-      <c r="S35" t="s">
+      <c r="T35" t="s">
         <v>72</v>
       </c>
-      <c r="T35" t="s">
+      <c r="U35" t="s">
         <v>83</v>
       </c>
-      <c r="U35" t="s">
+      <c r="V35" t="s">
         <v>84</v>
       </c>
-      <c r="V35" t="s">
+      <c r="W35" t="s">
         <v>83</v>
       </c>
-      <c r="W35" t="s">
+      <c r="X35" t="s">
         <v>84</v>
       </c>
-      <c r="X35" t="s">
+      <c r="Y35" t="s">
         <v>83</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="Z35" t="s">
         <v>85</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AA35" t="s">
         <v>94</v>
       </c>
-      <c r="AA35" t="s">
+      <c r="AB35" t="s">
         <v>85</v>
       </c>
-      <c r="AB35" t="s">
+      <c r="AC35" t="s">
         <v>95</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="AD35" t="s">
         <v>85</v>
       </c>
-      <c r="AD35" t="s">
+      <c r="AE35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -3117,17 +3201,17 @@
         <v>116</v>
       </c>
       <c r="G36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" t="s">
         <v>70</v>
       </c>
-      <c r="H36" t="s">
-        <v>65</v>
-      </c>
       <c r="I36" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" t="s">
         <v>70</v>
       </c>
-      <c r="J36" t="s">
-        <v>65</v>
-      </c>
       <c r="K36" t="s">
         <v>65</v>
       </c>
@@ -3138,58 +3222,61 @@
         <v>65</v>
       </c>
       <c r="N36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O36" t="s">
         <v>71</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>92</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>71</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>93</v>
       </c>
-      <c r="R36" t="s">
+      <c r="S36" t="s">
         <v>71</v>
       </c>
-      <c r="S36" t="s">
+      <c r="T36" t="s">
         <v>72</v>
       </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
         <v>83</v>
       </c>
-      <c r="U36" t="s">
+      <c r="V36" t="s">
         <v>84</v>
       </c>
-      <c r="V36" t="s">
+      <c r="W36" t="s">
         <v>83</v>
       </c>
-      <c r="W36" t="s">
+      <c r="X36" t="s">
         <v>84</v>
       </c>
-      <c r="X36" t="s">
+      <c r="Y36" t="s">
         <v>83</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="Z36" t="s">
         <v>85</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AA36" t="s">
         <v>94</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AB36" t="s">
         <v>85</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AC36" t="s">
         <v>95</v>
       </c>
-      <c r="AC36" t="s">
+      <c r="AD36" t="s">
         <v>85</v>
       </c>
-      <c r="AD36" t="s">
+      <c r="AE36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -3209,17 +3296,17 @@
         <v>116</v>
       </c>
       <c r="G37" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" t="s">
         <v>70</v>
       </c>
-      <c r="H37" t="s">
-        <v>65</v>
-      </c>
       <c r="I37" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" t="s">
         <v>70</v>
       </c>
-      <c r="J37" t="s">
-        <v>65</v>
-      </c>
       <c r="K37" t="s">
         <v>65</v>
       </c>
@@ -3230,58 +3317,61 @@
         <v>65</v>
       </c>
       <c r="N37" t="s">
+        <v>65</v>
+      </c>
+      <c r="O37" t="s">
         <v>71</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>92</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>71</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>93</v>
       </c>
-      <c r="R37" t="s">
+      <c r="S37" t="s">
         <v>71</v>
       </c>
-      <c r="S37" t="s">
+      <c r="T37" t="s">
         <v>72</v>
       </c>
-      <c r="T37" t="s">
+      <c r="U37" t="s">
         <v>83</v>
       </c>
-      <c r="U37" t="s">
+      <c r="V37" t="s">
         <v>84</v>
       </c>
-      <c r="V37" t="s">
+      <c r="W37" t="s">
         <v>83</v>
       </c>
-      <c r="W37" t="s">
+      <c r="X37" t="s">
         <v>84</v>
       </c>
-      <c r="X37" t="s">
+      <c r="Y37" t="s">
         <v>83</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="Z37" t="s">
         <v>85</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AA37" t="s">
         <v>94</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AB37" t="s">
         <v>85</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AC37" t="s">
         <v>95</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AD37" t="s">
         <v>85</v>
       </c>
-      <c r="AD37" t="s">
+      <c r="AE37" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -3301,17 +3391,17 @@
         <v>116</v>
       </c>
       <c r="G38" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" t="s">
         <v>70</v>
       </c>
-      <c r="H38" t="s">
-        <v>65</v>
-      </c>
       <c r="I38" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" t="s">
         <v>70</v>
       </c>
-      <c r="J38" t="s">
-        <v>65</v>
-      </c>
       <c r="K38" t="s">
         <v>65</v>
       </c>
@@ -3322,58 +3412,61 @@
         <v>65</v>
       </c>
       <c r="N38" t="s">
+        <v>65</v>
+      </c>
+      <c r="O38" t="s">
         <v>71</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>92</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>71</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>93</v>
       </c>
-      <c r="R38" t="s">
+      <c r="S38" t="s">
         <v>71</v>
       </c>
-      <c r="S38" t="s">
+      <c r="T38" t="s">
         <v>72</v>
       </c>
-      <c r="T38" t="s">
+      <c r="U38" t="s">
         <v>83</v>
       </c>
-      <c r="U38" t="s">
+      <c r="V38" t="s">
         <v>84</v>
       </c>
-      <c r="V38" t="s">
+      <c r="W38" t="s">
         <v>83</v>
       </c>
-      <c r="W38" t="s">
+      <c r="X38" t="s">
         <v>84</v>
       </c>
-      <c r="X38" t="s">
+      <c r="Y38" t="s">
         <v>83</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="Z38" t="s">
         <v>85</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AA38" t="s">
         <v>94</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>85</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AC38" t="s">
         <v>95</v>
       </c>
-      <c r="AC38" t="s">
+      <c r="AD38" t="s">
         <v>85</v>
       </c>
-      <c r="AD38" t="s">
+      <c r="AE38" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -3393,17 +3486,17 @@
         <v>116</v>
       </c>
       <c r="G39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" t="s">
         <v>70</v>
       </c>
-      <c r="H39" t="s">
-        <v>65</v>
-      </c>
       <c r="I39" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39" t="s">
         <v>70</v>
       </c>
-      <c r="J39" t="s">
-        <v>65</v>
-      </c>
       <c r="K39" t="s">
         <v>65</v>
       </c>
@@ -3414,58 +3507,61 @@
         <v>65</v>
       </c>
       <c r="N39" t="s">
+        <v>65</v>
+      </c>
+      <c r="O39" t="s">
         <v>71</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>92</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>71</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>93</v>
       </c>
-      <c r="R39" t="s">
+      <c r="S39" t="s">
         <v>71</v>
       </c>
-      <c r="S39" t="s">
+      <c r="T39" t="s">
         <v>72</v>
       </c>
-      <c r="T39" t="s">
+      <c r="U39" t="s">
         <v>83</v>
       </c>
-      <c r="U39" t="s">
+      <c r="V39" t="s">
         <v>84</v>
       </c>
-      <c r="V39" t="s">
+      <c r="W39" t="s">
         <v>83</v>
       </c>
-      <c r="W39" t="s">
+      <c r="X39" t="s">
         <v>84</v>
       </c>
-      <c r="X39" t="s">
+      <c r="Y39" t="s">
         <v>83</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="Z39" t="s">
         <v>85</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AA39" t="s">
         <v>94</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AB39" t="s">
         <v>85</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AC39" t="s">
         <v>95</v>
       </c>
-      <c r="AC39" t="s">
+      <c r="AD39" t="s">
         <v>85</v>
       </c>
-      <c r="AD39" t="s">
+      <c r="AE39" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -3485,16 +3581,16 @@
         <v>49</v>
       </c>
       <c r="G40" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H40" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I40" t="s">
         <v>75</v>
       </c>
       <c r="J40" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K40" t="s">
         <v>49</v>
@@ -3506,58 +3602,61 @@
         <v>49</v>
       </c>
       <c r="N40" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O40" t="s">
         <v>76</v>
       </c>
       <c r="P40" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q40" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R40" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S40" t="s">
+        <v>49</v>
+      </c>
+      <c r="T40" t="s">
         <v>73</v>
       </c>
-      <c r="T40" t="s">
-        <v>49</v>
-      </c>
       <c r="U40" t="s">
         <v>49</v>
       </c>
       <c r="V40" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W40" t="s">
         <v>75</v>
       </c>
       <c r="X40" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y40" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z40" t="s">
         <v>76</v>
       </c>
       <c r="AA40" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB40" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC40" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD40" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE40" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3577,16 +3676,16 @@
         <v>49</v>
       </c>
       <c r="G41" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H41" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I41" t="s">
         <v>75</v>
       </c>
       <c r="J41" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K41" t="s">
         <v>49</v>
@@ -3598,58 +3697,61 @@
         <v>49</v>
       </c>
       <c r="N41" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O41" t="s">
         <v>76</v>
       </c>
       <c r="P41" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q41" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R41" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S41" t="s">
+        <v>49</v>
+      </c>
+      <c r="T41" t="s">
         <v>73</v>
       </c>
-      <c r="T41" t="s">
-        <v>49</v>
-      </c>
       <c r="U41" t="s">
         <v>49</v>
       </c>
       <c r="V41" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W41" t="s">
         <v>75</v>
       </c>
       <c r="X41" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y41" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z41" t="s">
         <v>76</v>
       </c>
       <c r="AA41" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB41" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC41" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE41" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -3669,16 +3771,16 @@
         <v>49</v>
       </c>
       <c r="G42" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H42" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I42" t="s">
         <v>75</v>
       </c>
       <c r="J42" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K42" t="s">
         <v>49</v>
@@ -3690,58 +3792,61 @@
         <v>49</v>
       </c>
       <c r="N42" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O42" t="s">
         <v>76</v>
       </c>
       <c r="P42" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q42" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R42" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S42" t="s">
+        <v>49</v>
+      </c>
+      <c r="T42" t="s">
         <v>73</v>
       </c>
-      <c r="T42" t="s">
-        <v>49</v>
-      </c>
       <c r="U42" t="s">
         <v>49</v>
       </c>
       <c r="V42" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W42" t="s">
         <v>75</v>
       </c>
       <c r="X42" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y42" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z42" t="s">
         <v>76</v>
       </c>
       <c r="AA42" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB42" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC42" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD42" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE42" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -3761,16 +3866,16 @@
         <v>49</v>
       </c>
       <c r="G43" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H43" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I43" t="s">
         <v>75</v>
       </c>
       <c r="J43" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s">
         <v>49</v>
@@ -3782,58 +3887,61 @@
         <v>49</v>
       </c>
       <c r="N43" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O43" t="s">
         <v>76</v>
       </c>
       <c r="P43" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q43" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R43" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S43" t="s">
+        <v>49</v>
+      </c>
+      <c r="T43" t="s">
         <v>73</v>
       </c>
-      <c r="T43" t="s">
-        <v>49</v>
-      </c>
       <c r="U43" t="s">
         <v>49</v>
       </c>
       <c r="V43" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W43" t="s">
         <v>75</v>
       </c>
       <c r="X43" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y43" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z43" t="s">
         <v>76</v>
       </c>
       <c r="AA43" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB43" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC43" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE43" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -3853,16 +3961,16 @@
         <v>49</v>
       </c>
       <c r="G44" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H44" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I44" t="s">
         <v>75</v>
       </c>
       <c r="J44" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K44" t="s">
         <v>49</v>
@@ -3874,58 +3982,61 @@
         <v>49</v>
       </c>
       <c r="N44" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O44" t="s">
         <v>76</v>
       </c>
       <c r="P44" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q44" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R44" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S44" t="s">
+        <v>49</v>
+      </c>
+      <c r="T44" t="s">
         <v>73</v>
       </c>
-      <c r="T44" t="s">
-        <v>49</v>
-      </c>
       <c r="U44" t="s">
         <v>49</v>
       </c>
       <c r="V44" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W44" t="s">
         <v>75</v>
       </c>
       <c r="X44" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y44" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z44" t="s">
         <v>76</v>
       </c>
       <c r="AA44" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB44" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC44" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE44" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>68</v>
       </c>
@@ -3945,16 +4056,16 @@
         <v>49</v>
       </c>
       <c r="G45" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H45" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I45" t="s">
         <v>75</v>
       </c>
       <c r="J45" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s">
         <v>49</v>
@@ -3966,58 +4077,61 @@
         <v>49</v>
       </c>
       <c r="N45" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O45" t="s">
         <v>76</v>
       </c>
       <c r="P45" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q45" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R45" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S45" t="s">
+        <v>49</v>
+      </c>
+      <c r="T45" t="s">
         <v>73</v>
       </c>
-      <c r="T45" t="s">
-        <v>49</v>
-      </c>
       <c r="U45" t="s">
         <v>49</v>
       </c>
       <c r="V45" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W45" t="s">
         <v>75</v>
       </c>
       <c r="X45" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y45" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z45" t="s">
         <v>76</v>
       </c>
       <c r="AA45" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB45" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC45" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE45" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -4037,16 +4151,16 @@
         <v>49</v>
       </c>
       <c r="G46" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H46" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I46" t="s">
         <v>75</v>
       </c>
       <c r="J46" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K46" t="s">
         <v>49</v>
@@ -4058,58 +4172,61 @@
         <v>49</v>
       </c>
       <c r="N46" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O46" t="s">
         <v>76</v>
       </c>
       <c r="P46" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q46" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R46" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S46" t="s">
+        <v>49</v>
+      </c>
+      <c r="T46" t="s">
         <v>73</v>
       </c>
-      <c r="T46" t="s">
-        <v>49</v>
-      </c>
       <c r="U46" t="s">
         <v>49</v>
       </c>
       <c r="V46" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W46" t="s">
         <v>75</v>
       </c>
       <c r="X46" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y46" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z46" t="s">
         <v>76</v>
       </c>
       <c r="AA46" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB46" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC46" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD46" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE46" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -4129,16 +4246,16 @@
         <v>131</v>
       </c>
       <c r="G47" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="H47" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I47" t="s">
         <v>75</v>
       </c>
       <c r="J47" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K47" t="s">
         <v>49</v>
@@ -4150,58 +4267,61 @@
         <v>49</v>
       </c>
       <c r="N47" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O47" t="s">
         <v>76</v>
       </c>
       <c r="P47" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q47" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R47" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S47" t="s">
+        <v>49</v>
+      </c>
+      <c r="T47" t="s">
         <v>73</v>
       </c>
-      <c r="T47" t="s">
-        <v>49</v>
-      </c>
       <c r="U47" t="s">
         <v>49</v>
       </c>
       <c r="V47" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W47" t="s">
         <v>75</v>
       </c>
       <c r="X47" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y47" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z47" t="s">
         <v>76</v>
       </c>
       <c r="AA47" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB47" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC47" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD47" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE47" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -4221,16 +4341,16 @@
         <v>49</v>
       </c>
       <c r="G48" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H48" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I48" t="s">
         <v>75</v>
       </c>
       <c r="J48" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K48" t="s">
         <v>49</v>
@@ -4242,58 +4362,61 @@
         <v>49</v>
       </c>
       <c r="N48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O48" t="s">
         <v>76</v>
       </c>
       <c r="P48" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R48" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S48" t="s">
+        <v>49</v>
+      </c>
+      <c r="T48" t="s">
         <v>73</v>
       </c>
-      <c r="T48" t="s">
-        <v>49</v>
-      </c>
       <c r="U48" t="s">
         <v>49</v>
       </c>
       <c r="V48" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W48" t="s">
         <v>75</v>
       </c>
       <c r="X48" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z48" t="s">
         <v>76</v>
       </c>
       <c r="AA48" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC48" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD48" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE48" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -4313,16 +4436,16 @@
         <v>131</v>
       </c>
       <c r="G49" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="H49" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I49" t="s">
         <v>75</v>
       </c>
       <c r="J49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K49" t="s">
         <v>49</v>
@@ -4334,58 +4457,61 @@
         <v>49</v>
       </c>
       <c r="N49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O49" t="s">
         <v>76</v>
       </c>
       <c r="P49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S49" t="s">
+        <v>49</v>
+      </c>
+      <c r="T49" t="s">
         <v>73</v>
       </c>
-      <c r="T49" t="s">
-        <v>49</v>
-      </c>
       <c r="U49" t="s">
         <v>49</v>
       </c>
       <c r="V49" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W49" t="s">
         <v>75</v>
       </c>
       <c r="X49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z49" t="s">
         <v>76</v>
       </c>
       <c r="AA49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD49" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE49" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -4405,16 +4531,16 @@
         <v>131</v>
       </c>
       <c r="G50" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="H50" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I50" t="s">
         <v>75</v>
       </c>
       <c r="J50" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K50" t="s">
         <v>49</v>
@@ -4426,58 +4552,61 @@
         <v>49</v>
       </c>
       <c r="N50" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O50" t="s">
         <v>76</v>
       </c>
       <c r="P50" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q50" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R50" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S50" t="s">
+        <v>49</v>
+      </c>
+      <c r="T50" t="s">
         <v>73</v>
       </c>
-      <c r="T50" t="s">
-        <v>49</v>
-      </c>
       <c r="U50" t="s">
         <v>49</v>
       </c>
       <c r="V50" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W50" t="s">
         <v>75</v>
       </c>
       <c r="X50" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y50" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z50" t="s">
         <v>76</v>
       </c>
       <c r="AA50" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB50" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC50" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD50" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE50" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -4497,16 +4626,16 @@
         <v>49</v>
       </c>
       <c r="G51" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H51" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I51" t="s">
         <v>75</v>
       </c>
       <c r="J51" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K51" t="s">
         <v>49</v>
@@ -4518,58 +4647,61 @@
         <v>49</v>
       </c>
       <c r="N51" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O51" t="s">
         <v>76</v>
       </c>
       <c r="P51" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q51" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R51" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S51" t="s">
+        <v>49</v>
+      </c>
+      <c r="T51" t="s">
         <v>73</v>
       </c>
-      <c r="T51" t="s">
-        <v>49</v>
-      </c>
       <c r="U51" t="s">
         <v>49</v>
       </c>
       <c r="V51" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W51" t="s">
         <v>75</v>
       </c>
       <c r="X51" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y51" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z51" t="s">
         <v>76</v>
       </c>
       <c r="AA51" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB51" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC51" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD51" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE51" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -4589,16 +4721,16 @@
         <v>131</v>
       </c>
       <c r="G52" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="H52" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I52" t="s">
         <v>75</v>
       </c>
       <c r="J52" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K52" t="s">
         <v>49</v>
@@ -4610,58 +4742,61 @@
         <v>49</v>
       </c>
       <c r="N52" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O52" t="s">
         <v>76</v>
       </c>
       <c r="P52" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q52" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R52" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S52" t="s">
+        <v>49</v>
+      </c>
+      <c r="T52" t="s">
         <v>73</v>
       </c>
-      <c r="T52" t="s">
-        <v>49</v>
-      </c>
       <c r="U52" t="s">
         <v>49</v>
       </c>
       <c r="V52" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W52" t="s">
         <v>75</v>
       </c>
       <c r="X52" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y52" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z52" t="s">
         <v>76</v>
       </c>
       <c r="AA52" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB52" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC52" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD52" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE52" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -4681,16 +4816,16 @@
         <v>131</v>
       </c>
       <c r="G53" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="H53" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I53" t="s">
         <v>75</v>
       </c>
       <c r="J53" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K53" t="s">
         <v>49</v>
@@ -4702,58 +4837,61 @@
         <v>49</v>
       </c>
       <c r="N53" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O53" t="s">
         <v>76</v>
       </c>
       <c r="P53" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q53" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R53" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S53" t="s">
+        <v>49</v>
+      </c>
+      <c r="T53" t="s">
         <v>73</v>
       </c>
-      <c r="T53" t="s">
-        <v>49</v>
-      </c>
       <c r="U53" t="s">
         <v>49</v>
       </c>
       <c r="V53" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W53" t="s">
         <v>75</v>
       </c>
       <c r="X53" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y53" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z53" t="s">
         <v>76</v>
       </c>
       <c r="AA53" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB53" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC53" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE53" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -4773,16 +4911,16 @@
         <v>49</v>
       </c>
       <c r="G54" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H54" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I54" t="s">
         <v>75</v>
       </c>
       <c r="J54" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K54" t="s">
         <v>49</v>
@@ -4794,58 +4932,61 @@
         <v>49</v>
       </c>
       <c r="N54" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O54" t="s">
         <v>76</v>
       </c>
       <c r="P54" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q54" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R54" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S54" t="s">
+        <v>49</v>
+      </c>
+      <c r="T54" t="s">
         <v>73</v>
       </c>
-      <c r="T54" t="s">
-        <v>49</v>
-      </c>
       <c r="U54" t="s">
         <v>49</v>
       </c>
       <c r="V54" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W54" t="s">
         <v>75</v>
       </c>
       <c r="X54" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y54" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z54" t="s">
         <v>76</v>
       </c>
       <c r="AA54" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB54" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC54" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD54" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE54" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -4865,16 +5006,16 @@
         <v>49</v>
       </c>
       <c r="G55" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H55" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I55" t="s">
         <v>75</v>
       </c>
       <c r="J55" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K55" t="s">
         <v>49</v>
@@ -4886,58 +5027,61 @@
         <v>49</v>
       </c>
       <c r="N55" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O55" t="s">
         <v>76</v>
       </c>
       <c r="P55" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q55" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R55" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S55" t="s">
+        <v>49</v>
+      </c>
+      <c r="T55" t="s">
         <v>73</v>
       </c>
-      <c r="T55" t="s">
-        <v>49</v>
-      </c>
       <c r="U55" t="s">
         <v>49</v>
       </c>
       <c r="V55" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W55" t="s">
         <v>75</v>
       </c>
       <c r="X55" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y55" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z55" t="s">
         <v>76</v>
       </c>
       <c r="AA55" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB55" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC55" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD55" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE55" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -4957,16 +5101,16 @@
         <v>49</v>
       </c>
       <c r="G56" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="H56" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I56" t="s">
         <v>75</v>
       </c>
       <c r="J56" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="K56" t="s">
         <v>49</v>
@@ -4978,58 +5122,61 @@
         <v>49</v>
       </c>
       <c r="N56" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="O56" t="s">
         <v>76</v>
       </c>
       <c r="P56" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="Q56" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="R56" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="S56" t="s">
+        <v>49</v>
+      </c>
+      <c r="T56" t="s">
         <v>73</v>
       </c>
-      <c r="T56" t="s">
-        <v>49</v>
-      </c>
       <c r="U56" t="s">
         <v>49</v>
       </c>
       <c r="V56" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="W56" t="s">
         <v>75</v>
       </c>
       <c r="X56" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="Y56" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="Z56" t="s">
         <v>76</v>
       </c>
       <c r="AA56" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AB56" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="AC56" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AD56" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE56" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>117</v>
       </c>
@@ -5048,8 +5195,11 @@
       <c r="F57" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="G57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>119</v>
       </c>
@@ -5068,8 +5218,11 @@
       <c r="F58" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="G58" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>120</v>
       </c>
@@ -5088,8 +5241,11 @@
       <c r="F59" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="G59" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>121</v>
       </c>
@@ -5108,10 +5264,13 @@
       <c r="F60" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="G60" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M39" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M39">
+  <autoFilter ref="A1:N39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N39">
       <sortCondition ref="B1:B39"/>
     </sortState>
   </autoFilter>
